--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -49,6 +49,32 @@
         <t xml:space="preserve">Legend
 🟠 Orange – SELL
 🔵 Blue – BUY</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B8">
+      <text>
+        <t xml:space="preserve">Target Calculation Logic:
+1. Base Target:
+   - LONG:
+     • NSE Topers - AllSec  → 3.5/B7
+     • NSE Topers - NEXT50 → 3.0/B7
+     • EVB                  → 2.25/B7
+   - SHORT:
+     • Fixed base target   → 2.25/B7
+2. Participation Adjustment:
+   - If participation is Strong:
+     • LONG  → +1.5/B7
+     • SHORT → +1.0/B7
+   - Otherwise → +0
+3. Market Order Adjustment:
+   - If entry is a Market order → +0.25/B7
+   - This accounts for expected slippage from using a Market order.
+   - Otherwise → +0
+4. Final Target:
+   - Base Target
+     + Participation Adjustment
+     + Market Order Adjustment
+   - Final value is rounded UP to the nearest 0.25 using CEILING().</t>
       </text>
     </comment>
   </commentList>
@@ -154,7 +180,7 @@
     <t>*  Setup</t>
   </si>
   <si>
-    <t>NSE Topers</t>
+    <t>NSE Topers - AllSec</t>
   </si>
   <si>
     <t>Select Setup: Different setups use different target values based on backtesting.</t>
@@ -1675,7 +1701,8 @@
         <v>7</v>
       </c>
       <c r="B5" s="16">
-        <v>0.025</v>
+        <f>IF(AND(ISNUMBER(SEARCH("NSE Topers",B19)),B18="Long"),0.03,0.02)</f>
+        <v>0.03</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>8</v>
@@ -1778,19 +1805,32 @@
       </c>
       <c r="B8" s="23">
         <f>CEILING(
-IFS(
-B19="NSE Topers",3/B7,
-B19="EMB",2/B7,
-B19="EVB",2.25/B7
-)
-+IF(B25="Strong",1/B7,0)
-+IF(B24="Market",0.5,0),
-0.25)</f>
-        <v>6.5</v>
+    IF(
+        B18="Long",
+        IFS(
+            B19="NSE Topers - AllSec",3.5/B7,
+            B19="NSE Topers - NEXT50",3/B7,
+            B19="EVB",2.25/B7
+        ),
+        2.25/B7
+    )
+    +IF(
+        AND(B25="Strong",B18="Long"),
+        1.5/B7,
+        IF(
+            AND(B25="Strong",B18="Short"),
+            1/B7,
+            0
+        )
+    )
+    +IF(B24="Market",0.25/B7,0),
+    0.25
+)</f>
+        <v>7.5</v>
       </c>
       <c r="C8" s="24" t="str">
         <f t="shared" ref="C8:C9" si="1">B8 &amp; "R"</f>
-        <v>6.5R</v>
+        <v>7.5R</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -1821,13 +1861,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="28">
-        <f>CEILING(B8*2.5,1)
+        <f>CEILING(B8*2,1)
  </f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>17R</v>
+        <v>15R</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -1858,7 +1898,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="29">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>16</v>
@@ -1926,7 +1966,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="33">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>20</v>
@@ -1994,7 +2034,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="38">
-        <v>0.02</v>
+        <v>0.0125</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="7"/>
@@ -2027,7 +2067,7 @@
       </c>
       <c r="B15" s="40">
         <f>B4*B5</f>
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="C15" s="37"/>
       <c r="D15" s="7"/>
@@ -2555,7 +2595,7 @@
       </c>
       <c r="B31" s="63">
         <f>B4*B5</f>
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>52</v>
@@ -30455,14 +30495,14 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B18">
       <formula1>"Long,Short"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B19">
-      <formula1>"NSE Topers,EMB,EVB"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B24">
       <formula1>"Limit,Market"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B25">
       <formula1>"Normal,Strong"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B19">
+      <formula1>"NSE Topers - AllSec,NSE Topers - NEXT50,EVB"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -58,9 +58,9 @@
    - LONG:
      • NSE Topers - AllSec  → 3.5/B7
      • NSE Topers - NEXT50 → 3.0/B7
-     • EVB                  → 2.25/B7
+     • EVB                  → 2.5/B7
    - SHORT:
-     • Fixed base target   → 2.25/B7
+     • Fixed base target   → 2.0/B7
 2. Participation Adjustment:
    - If participation is Strong:
      • LONG  → +1.5/B7
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>📊  Position Size Calculator ( Fill in the required fields marked with * )</t>
   </si>
@@ -108,7 +108,7 @@
     <t>Max Risk Per Trade (%)</t>
   </si>
   <si>
-    <t>% of capital at risk (default 2%)</t>
+    <t>% of capital at risk (default 2% for SHORT and 2.5% for LONG)</t>
   </si>
   <si>
     <t>Intraday Leverage Multiplier</t>
@@ -165,6 +165,9 @@
     <t>*  Symbol</t>
   </si>
   <si>
+    <t>ATGL</t>
+  </si>
+  <si>
     <t>Stock Name: Enter the stock name (not case-sensitive). It will be converted to UPPERCASE automatically.</t>
   </si>
   <si>
@@ -180,7 +183,7 @@
     <t>*  Setup</t>
   </si>
   <si>
-    <t>NSE Topers - AllSec</t>
+    <t>EVB</t>
   </si>
   <si>
     <t>Select Setup: Different setups use different target values based on backtesting.</t>
@@ -214,7 +217,7 @@
     <t>* Participation ( Volume )</t>
   </si>
   <si>
-    <t>Normal</t>
+    <t>Strong</t>
   </si>
   <si>
     <r>
@@ -1012,11 +1015,11 @@
     <xf borderId="9" fillId="5" fontId="11" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="9" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="9" fillId="5" fontId="11" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1696,15 +1699,15 @@
       <c r="Y4" s="7"/>
       <c r="Z4" s="8"/>
     </row>
-    <row r="5" ht="21.75" hidden="1" customHeight="1">
+    <row r="5" ht="21.75" customHeight="1">
       <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="16">
-        <f>IF(AND(ISNUMBER(SEARCH("NSE Topers",B19)),B18="Long"),0.03,0.02)</f>
+        <f>IF(B18="Short",0.025,IF(AND(ISNUMBER(SEARCH("NSE Topers",B19)),B18="Long"),0.04,0.03))</f>
         <v>0.03</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="7"/>
@@ -1731,14 +1734,14 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="8"/>
     </row>
-    <row r="6" ht="30.0" hidden="1" customHeight="1">
+    <row r="6" ht="30.0" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <v>4.75</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="7"/>
@@ -1765,7 +1768,7 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" ht="21.75" hidden="1" customHeight="1">
+    <row r="7" ht="21.75" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
@@ -1799,7 +1802,7 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="8"/>
     </row>
-    <row r="8" ht="21.75" hidden="1" customHeight="1">
+    <row r="8" ht="21.75" customHeight="1">
       <c r="A8" s="22" t="s">
         <v>13</v>
       </c>
@@ -1810,9 +1813,9 @@
         IFS(
             B19="NSE Topers - AllSec",3.5/B7,
             B19="NSE Topers - NEXT50",3/B7,
-            B19="EVB",2.25/B7
+            B19="EVB",2/B7
         ),
-        2.25/B7
+        2/B7
     )
     +IF(
         AND(B25="Strong",B18="Long"),
@@ -1856,7 +1859,7 @@
       <c r="Y8" s="25"/>
       <c r="Z8" s="26"/>
     </row>
-    <row r="9" ht="21.75" hidden="1" customHeight="1">
+    <row r="9" ht="21.75" customHeight="1">
       <c r="A9" s="27" t="s">
         <v>14</v>
       </c>
@@ -1893,7 +1896,7 @@
       <c r="Y9" s="25"/>
       <c r="Z9" s="26"/>
     </row>
-    <row r="10" ht="21.75" hidden="1" customHeight="1">
+    <row r="10" ht="21.75" customHeight="1">
       <c r="A10" s="27" t="s">
         <v>15</v>
       </c>
@@ -1927,7 +1930,7 @@
       <c r="Y10" s="25"/>
       <c r="Z10" s="26"/>
     </row>
-    <row r="11" ht="21.75" hidden="1" customHeight="1">
+    <row r="11" ht="21.75" customHeight="1">
       <c r="A11" s="30" t="s">
         <v>17</v>
       </c>
@@ -1961,7 +1964,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" ht="21.75" hidden="1" customHeight="1">
+    <row r="12" ht="21.75" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>19</v>
       </c>
@@ -1995,7 +1998,7 @@
       <c r="Y12" s="25"/>
       <c r="Z12" s="26"/>
     </row>
-    <row r="13" ht="21.75" hidden="1" customHeight="1">
+    <row r="13" ht="21.75" customHeight="1">
       <c r="A13" s="35" t="s">
         <v>21</v>
       </c>
@@ -2029,7 +2032,7 @@
       <c r="Y13" s="7"/>
       <c r="Z13" s="8"/>
     </row>
-    <row r="14" ht="21.75" hidden="1" customHeight="1">
+    <row r="14" ht="21.75" customHeight="1">
       <c r="A14" s="35" t="s">
         <v>23</v>
       </c>
@@ -2128,9 +2131,11 @@
       <c r="A17" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
+      <c r="B17" s="44" t="s">
+        <v>27</v>
+      </c>
       <c r="C17" s="34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -2158,13 +2163,13 @@
     </row>
     <row r="18" ht="46.5" customHeight="1">
       <c r="A18" s="43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
@@ -2192,13 +2197,13 @@
     </row>
     <row r="19" ht="46.5" customHeight="1">
       <c r="A19" s="45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -2229,9 +2234,11 @@
         <f>IF(B18="Long", "*  Entry Candle High", "*  Entry Candle Low")</f>
         <v>*  Entry Candle High</v>
       </c>
-      <c r="B20" s="49"/>
+      <c r="B20" s="49">
+        <v>613.65</v>
+      </c>
       <c r="C20" s="50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -2259,11 +2266,13 @@
     </row>
     <row r="21" ht="36.75" customHeight="1">
       <c r="A21" s="51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="18" t="s">
-        <v>36</v>
+      <c r="B21" s="52">
+        <v>3.48</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -2291,9 +2300,11 @@
     </row>
     <row r="22" ht="52.5" customHeight="1">
       <c r="A22" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
-      <c r="B22" s="54"/>
+      <c r="B22" s="54">
+        <v>0.2</v>
+      </c>
       <c r="C22" s="14"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -2324,9 +2335,11 @@
         <f>IF(B18="Long","* Upper Circuit","* Lower Circuit")</f>
         <v>* Upper Circuit</v>
       </c>
-      <c r="B23" s="54"/>
+      <c r="B23" s="54">
+        <v>1000.0</v>
+      </c>
       <c r="C23" s="55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -2354,13 +2367,13 @@
     </row>
     <row r="24" ht="46.5" customHeight="1">
       <c r="A24" s="53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -2388,13 +2401,13 @@
     </row>
     <row r="25" ht="93.0" customHeight="1">
       <c r="A25" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -2422,11 +2435,11 @@
     </row>
     <row r="26" ht="46.5" hidden="1" customHeight="1">
       <c r="A26" s="58" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B26" s="59">
         <f>IF(AND(B21&gt;0, B22&gt;0), B22/B21,0)</f>
-        <v>0</v>
+        <v>0.05747126437</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="7"/>
@@ -2455,7 +2468,7 @@
     </row>
     <row r="27" ht="46.5" hidden="1" customHeight="1">
       <c r="A27" s="58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" s="60">
         <f>IF(B20&lt;1,0,
@@ -2464,9 +2477,9 @@
  IF(B20&lt;=5000,0.1,
  IF(B20&lt;=10000,0.5,
  IF(B20&lt;=20000,1,5))))))</f>
-        <v>0</v>
+        <v>0.05</v>
       </c>
-      <c r="C27" s="18"/>
+      <c r="C27" s="17"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -2493,13 +2506,13 @@
     </row>
     <row r="28" ht="46.5" hidden="1" customHeight="1">
       <c r="A28" s="61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" s="62">
         <f>IF(ISNUMBER(B20),B20,0)</f>
-        <v>0</v>
+        <v>613.65</v>
       </c>
-      <c r="C28" s="18"/>
+      <c r="C28" s="17"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -2526,7 +2539,7 @@
     </row>
     <row r="29" ht="21.75" hidden="1" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -2556,14 +2569,14 @@
     </row>
     <row r="30" ht="21.75" hidden="1" customHeight="1">
       <c r="A30" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="63">
         <f>FLOOR(B21*B7, 0.1)</f>
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -2591,14 +2604,14 @@
     </row>
     <row r="31" ht="33.0" hidden="1" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31" s="63">
         <f>B4*B5</f>
         <v>15000</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -2626,14 +2639,14 @@
     </row>
     <row r="32" ht="21.75" hidden="1" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="63">
         <f>B4*B6</f>
         <v>2375000</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -2661,14 +2674,14 @@
     </row>
     <row r="33" ht="21.75" hidden="1" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" s="64">
         <f>IF(B30&gt;0,B31/B30,0)</f>
-        <v>0</v>
+        <v>8823.529412</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -2696,14 +2709,14 @@
     </row>
     <row r="34" ht="21.75" hidden="1" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B34" s="64">
         <f>IF(B28&gt;0, B32/B28, 0)</f>
-        <v>0</v>
+        <v>3870.284364</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -2731,14 +2744,14 @@
     </row>
     <row r="35" ht="21.75" hidden="1" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B35" s="65">
         <f>MIN(B33,B34)</f>
-        <v>0</v>
+        <v>3870.284364</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -2766,7 +2779,7 @@
     </row>
     <row r="36" ht="21.75" hidden="1" customHeight="1">
       <c r="A36" s="66" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36" s="67" t="b">
         <f>B26&gt;B11</f>
@@ -2799,7 +2812,7 @@
     </row>
     <row r="37" ht="21.75" hidden="1" customHeight="1">
       <c r="A37" s="66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B37" s="67" t="b">
         <f>IF(B23&lt;1,FALSE,IF(B18="Long",(B23-B47)/B23&lt;=B14,(B47-B23)/B23&lt;=B14))</f>
@@ -2832,7 +2845,7 @@
     </row>
     <row r="38" ht="21.75" hidden="1" customHeight="1">
       <c r="A38" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B38" s="67" t="b">
         <f>IF(B23&lt;1,FALSE,IF(B18="Long",(B23-B48)/B23&lt;=B14,(B48-B23)/B23&lt;=B14))</f>
@@ -2907,7 +2920,7 @@
     </row>
     <row r="40" ht="40.5" customHeight="1">
       <c r="A40" s="71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B40" s="72"/>
       <c r="C40" s="73"/>
@@ -2937,11 +2950,11 @@
     </row>
     <row r="41" ht="30.75" customHeight="1">
       <c r="A41" s="74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B41" s="75" t="str">
         <f>B17</f>
-        <v/>
+        <v>ATGL</v>
       </c>
       <c r="C41" s="76"/>
       <c r="D41" s="7"/>
@@ -2970,14 +2983,14 @@
     </row>
     <row r="42" ht="35.25" customHeight="1">
       <c r="A42" s="77" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B42" s="78">
         <f>IFERROR(IF(OR(B36,B37),0,IF(B35&gt;5,ROUND(B35/5,0)*5,B35)), 0)</f>
-        <v>0</v>
+        <v>3870</v>
       </c>
       <c r="C42" s="79" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -3005,7 +3018,7 @@
     </row>
     <row r="43" ht="41.25" customHeight="1">
       <c r="A43" s="80" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B43" s="81">
         <f>IFS(
@@ -3013,10 +3026,10 @@
     B18="Long", B28+B10*B27,
     B18="Short", B28-B10*B27
 )</f>
-        <v>0</v>
+        <v>613.8</v>
       </c>
       <c r="C43" s="79" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -3044,7 +3057,7 @@
     </row>
     <row r="44" ht="43.5" hidden="1" customHeight="1">
       <c r="A44" s="80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B44" s="81" t="str">
         <f>if(B24="Limit", CEILING(B43+B27*B10, B27), "")</f>
@@ -3077,7 +3090,7 @@
     </row>
     <row r="45" ht="43.5" customHeight="1">
       <c r="A45" s="80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B45" s="81">
         <f>LET(
@@ -3091,10 +3104,10 @@
     "⚠️ N/A"
   )
 )</f>
-        <v>0</v>
+        <v>610.9</v>
       </c>
       <c r="C45" s="82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -3122,7 +3135,7 @@
     </row>
     <row r="46" ht="43.5" customHeight="1">
       <c r="A46" s="80" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B46" s="81">
         <f>LET(
@@ -3133,10 +3146,10 @@
     CEILING(entryPrice+B30,B27)
   )
 )</f>
-        <v>0</v>
+        <v>612.1</v>
       </c>
       <c r="C46" s="79" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -3164,7 +3177,7 @@
     </row>
     <row r="47" ht="43.5" customHeight="1">
       <c r="A47" s="80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B47" s="81">
         <f>LET(
@@ -3176,10 +3189,10 @@
     )
   )
 </f>
-        <v>0</v>
+        <v>626.55</v>
       </c>
       <c r="C47" s="79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -3207,7 +3220,7 @@
     </row>
     <row r="48" ht="51.0" customHeight="1">
       <c r="A48" s="80" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B48" s="81">
         <f>LET(
@@ -3219,10 +3232,10 @@
     )
   )
 </f>
-        <v>0</v>
+        <v>639.3</v>
       </c>
       <c r="C48" s="82" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -3250,14 +3263,14 @@
     </row>
     <row r="49" ht="36.0" customHeight="1">
       <c r="A49" s="77" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B49" s="78">
         <f>IF(OR(B36,B37, B38),0,ROUND(B12*B42,0))</f>
-        <v>0</v>
+        <v>2129</v>
       </c>
       <c r="C49" s="82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -3285,14 +3298,14 @@
     </row>
     <row r="50" ht="36.0" customHeight="1">
       <c r="A50" s="77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B50" s="78">
         <f>IF(OR(B36,B37,B38),0,B42-B49)</f>
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="C50" s="82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -3320,14 +3333,14 @@
     </row>
     <row r="51" ht="36.0" customHeight="1">
       <c r="A51" s="80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B51" s="83">
         <f>IF(B18="Long",ROUND((B43-B46)*B42,0),ROUND((B46-B43)*B42,0))</f>
-        <v>0</v>
+        <v>6579</v>
       </c>
       <c r="C51" s="79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -3355,14 +3368,14 @@
     </row>
     <row r="52" ht="36.0" customHeight="1">
       <c r="A52" s="80" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B52" s="84" t="str">
         <f>ROUND(B51/B15,1) &amp; "R"</f>
-        <v>0R</v>
+        <v>0.4R</v>
       </c>
       <c r="C52" s="82" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -3390,14 +3403,14 @@
     </row>
     <row r="53" ht="36.0" customHeight="1">
       <c r="A53" s="85" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B53" s="86">
         <f>IF(B19="Long",ROUND((B45-B43)*B42,0),ROUND((B45-B43)*B42,0))</f>
-        <v>0</v>
+        <v>-11223</v>
       </c>
       <c r="C53" s="82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -3425,14 +3438,14 @@
     </row>
     <row r="54" ht="36.0" customHeight="1">
       <c r="A54" s="87" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B54" s="88" t="str">
         <f>ROUND(B53/B15,1) &amp; "R"</f>
-        <v>0R</v>
+        <v>-0.7R</v>
       </c>
       <c r="C54" s="89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
@@ -3460,14 +3473,14 @@
     </row>
     <row r="55" ht="36.0" customHeight="1">
       <c r="A55" s="87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B55" s="90">
         <f>IF(B18="Long",(B47-B43)*B42,(B43-B47)*B42)</f>
-        <v>0</v>
+        <v>49342.5</v>
       </c>
       <c r="C55" s="91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -3495,14 +3508,14 @@
     </row>
     <row r="56" ht="36.0" customHeight="1">
       <c r="A56" s="87" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B56" s="92" t="str">
         <f>ROUND(B55/B15,1) &amp; "R"</f>
-        <v>0R</v>
+        <v>3.3R</v>
       </c>
       <c r="C56" s="89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -3530,14 +3543,14 @@
     </row>
     <row r="57" ht="36.0" customHeight="1">
       <c r="A57" s="87" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B57" s="90">
         <f>IF(B18="Long",(B47-B43)*B49+(B48-B43)*B50,(B43-B47)*B49+(B43-B48)*B50)</f>
-        <v>0</v>
+        <v>71540.25</v>
       </c>
       <c r="C57" s="89" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -3565,14 +3578,14 @@
     </row>
     <row r="58" ht="36.0" customHeight="1">
       <c r="A58" s="93" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B58" s="94" t="str">
         <f>ROUND(B57/B15,1) &amp; "R"</f>
-        <v>0R</v>
+        <v>4.8R</v>
       </c>
       <c r="C58" s="95" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -165,7 +165,7 @@
     <t>*  Symbol</t>
   </si>
   <si>
-    <t>ATGL</t>
+    <t>SAMBHV</t>
   </si>
   <si>
     <t>Stock Name: Enter the stock name (not case-sensitive). It will be converted to UPPERCASE automatically.</t>
@@ -174,7 +174,7 @@
     <t>*  Trade Type</t>
   </si>
   <si>
-    <t>Long</t>
+    <t>Short</t>
   </si>
   <si>
     <t>Trade Direction: Select LONG or SHORT. SL and target prices are computed accordingly.</t>
@@ -217,7 +217,7 @@
     <t>* Participation ( Volume )</t>
   </si>
   <si>
-    <t>Strong</t>
+    <t>Normal</t>
   </si>
   <si>
     <r>
@@ -1699,13 +1699,13 @@
       <c r="Y4" s="7"/>
       <c r="Z4" s="8"/>
     </row>
-    <row r="5" ht="21.75" customHeight="1">
+    <row r="5" ht="21.75" hidden="1" customHeight="1">
       <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="16">
-        <f>IF(B18="Short",0.025,IF(AND(ISNUMBER(SEARCH("NSE Topers",B19)),B18="Long"),0.04,0.03))</f>
-        <v>0.03</v>
+        <f>IF(B18="Short",0.02,IF(AND(ISNUMBER(SEARCH("NSE Topers",B19)),B18="Long"),0.03,0.025))</f>
+        <v>0.02</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>8</v>
@@ -1734,7 +1734,7 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="8"/>
     </row>
-    <row r="6" ht="30.0" customHeight="1">
+    <row r="6" ht="30.0" hidden="1" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>9</v>
       </c>
@@ -1768,7 +1768,7 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" ht="21.75" customHeight="1">
+    <row r="7" ht="21.75" hidden="1" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
@@ -1802,7 +1802,7 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="8"/>
     </row>
-    <row r="8" ht="21.75" customHeight="1">
+    <row r="8" ht="21.75" hidden="1" customHeight="1">
       <c r="A8" s="22" t="s">
         <v>13</v>
       </c>
@@ -1815,7 +1815,7 @@
             B19="NSE Topers - NEXT50",3/B7,
             B19="EVB",2/B7
         ),
-        2/B7
+        1.75/B7
     )
     +IF(
         AND(B25="Strong",B18="Long"),
@@ -1829,11 +1829,11 @@
     +IF(B24="Market",0.25/B7,0),
     0.25
 )</f>
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="24" t="str">
         <f t="shared" ref="C8:C9" si="1">B8 &amp; "R"</f>
-        <v>7.5R</v>
+        <v>4R</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -1859,18 +1859,18 @@
       <c r="Y8" s="25"/>
       <c r="Z8" s="26"/>
     </row>
-    <row r="9" ht="21.75" customHeight="1">
+    <row r="9" ht="21.75" hidden="1" customHeight="1">
       <c r="A9" s="27" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="28">
         <f>CEILING(B8*2,1)
  </f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>15R</v>
+        <v>8R</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -1896,7 +1896,7 @@
       <c r="Y9" s="25"/>
       <c r="Z9" s="26"/>
     </row>
-    <row r="10" ht="21.75" customHeight="1">
+    <row r="10" ht="21.75" hidden="1" customHeight="1">
       <c r="A10" s="27" t="s">
         <v>15</v>
       </c>
@@ -1930,7 +1930,7 @@
       <c r="Y10" s="25"/>
       <c r="Z10" s="26"/>
     </row>
-    <row r="11" ht="21.75" customHeight="1">
+    <row r="11" ht="21.75" hidden="1" customHeight="1">
       <c r="A11" s="30" t="s">
         <v>17</v>
       </c>
@@ -1964,7 +1964,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" ht="21.75" customHeight="1">
+    <row r="12" ht="21.75" hidden="1" customHeight="1">
       <c r="A12" s="22" t="s">
         <v>19</v>
       </c>
@@ -1998,12 +1998,12 @@
       <c r="Y12" s="25"/>
       <c r="Z12" s="26"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1">
+    <row r="13" ht="21.75" hidden="1" customHeight="1">
       <c r="A13" s="35" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="36">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="C13" s="37" t="s">
         <v>22</v>
@@ -2032,7 +2032,7 @@
       <c r="Y13" s="7"/>
       <c r="Z13" s="8"/>
     </row>
-    <row r="14" ht="21.75" customHeight="1">
+    <row r="14" ht="21.75" hidden="1" customHeight="1">
       <c r="A14" s="35" t="s">
         <v>23</v>
       </c>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B15" s="40">
         <f>B4*B5</f>
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="C15" s="37"/>
       <c r="D15" s="7"/>
@@ -2232,10 +2232,10 @@
     <row r="20" ht="46.5" customHeight="1">
       <c r="A20" s="48" t="str">
         <f>IF(B18="Long", "*  Entry Candle High", "*  Entry Candle Low")</f>
-        <v>*  Entry Candle High</v>
+        <v>*  Entry Candle Low</v>
       </c>
       <c r="B20" s="49">
-        <v>613.65</v>
+        <v>155.61</v>
       </c>
       <c r="C20" s="50" t="s">
         <v>35</v>
@@ -2269,7 +2269,7 @@
         <v>36</v>
       </c>
       <c r="B21" s="52">
-        <v>3.48</v>
+        <v>2.18</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>37</v>
@@ -2303,7 +2303,7 @@
         <v>38</v>
       </c>
       <c r="B22" s="54">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="7"/>
@@ -2333,10 +2333,10 @@
     <row r="23" ht="52.5" customHeight="1">
       <c r="A23" s="53" t="str">
         <f>IF(B18="Long","* Upper Circuit","* Lower Circuit")</f>
-        <v>* Upper Circuit</v>
+        <v>* Lower Circuit</v>
       </c>
       <c r="B23" s="54">
-        <v>1000.0</v>
+        <v>118.0</v>
       </c>
       <c r="C23" s="55" t="s">
         <v>39</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B26" s="59">
         <f>IF(AND(B21&gt;0, B22&gt;0), B22/B21,0)</f>
-        <v>0.05747126437</v>
+        <v>0.04587155963</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="7"/>
@@ -2477,7 +2477,7 @@
  IF(B20&lt;=5000,0.1,
  IF(B20&lt;=10000,0.5,
  IF(B20&lt;=20000,1,5))))))</f>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="7"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B28" s="62">
         <f>IF(ISNUMBER(B20),B20,0)</f>
-        <v>613.65</v>
+        <v>155.61</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="7"/>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="B30" s="63">
         <f>FLOOR(B21*B7, 0.1)</f>
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>51</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B31" s="63">
         <f>B4*B5</f>
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>53</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B33" s="64">
         <f>IF(B30&gt;0,B31/B30,0)</f>
-        <v>8823.529412</v>
+        <v>10000</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>57</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B34" s="64">
         <f>IF(B28&gt;0, B32/B28, 0)</f>
-        <v>3870.284364</v>
+        <v>15262.51526</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>59</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B35" s="65">
         <f>MIN(B33,B34)</f>
-        <v>3870.284364</v>
+        <v>10000</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>61</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B41" s="75" t="str">
         <f>B17</f>
-        <v>ATGL</v>
+        <v>SAMBHV</v>
       </c>
       <c r="C41" s="76"/>
       <c r="D41" s="7"/>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="B42" s="78">
         <f>IFERROR(IF(OR(B36,B37),0,IF(B35&gt;5,ROUND(B35/5,0)*5,B35)), 0)</f>
-        <v>3870</v>
+        <v>10000</v>
       </c>
       <c r="C42" s="79" t="s">
         <v>68</v>
@@ -3026,7 +3026,7 @@
     B18="Long", B28+B10*B27,
     B18="Short", B28-B10*B27
 )</f>
-        <v>613.8</v>
+        <v>155.58</v>
       </c>
       <c r="C43" s="79" t="s">
         <v>70</v>
@@ -3104,7 +3104,7 @@
     "⚠️ N/A"
   )
 )</f>
-        <v>610.9</v>
+        <v>157.33</v>
       </c>
       <c r="C45" s="82" t="s">
         <v>73</v>
@@ -3146,7 +3146,7 @@
     CEILING(entryPrice+B30,B27)
   )
 )</f>
-        <v>612.1</v>
+        <v>156.58</v>
       </c>
       <c r="C46" s="79" t="s">
         <v>75</v>
@@ -3189,7 +3189,7 @@
     )
   )
 </f>
-        <v>626.55</v>
+        <v>151.58</v>
       </c>
       <c r="C47" s="79" t="s">
         <v>77</v>
@@ -3232,7 +3232,7 @@
     )
   )
 </f>
-        <v>639.3</v>
+        <v>147.58</v>
       </c>
       <c r="C48" s="82" t="s">
         <v>79</v>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B49" s="78">
         <f>IF(OR(B36,B37, B38),0,ROUND(B12*B42,0))</f>
-        <v>2129</v>
+        <v>5500</v>
       </c>
       <c r="C49" s="82" t="s">
         <v>81</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B50" s="78">
         <f>IF(OR(B36,B37,B38),0,B42-B49)</f>
-        <v>1741</v>
+        <v>4500</v>
       </c>
       <c r="C50" s="82" t="s">
         <v>83</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B51" s="83">
         <f>IF(B18="Long",ROUND((B43-B46)*B42,0),ROUND((B46-B43)*B42,0))</f>
-        <v>6579</v>
+        <v>10000</v>
       </c>
       <c r="C51" s="79" t="s">
         <v>85</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B52" s="84" t="str">
         <f>ROUND(B51/B15,1) &amp; "R"</f>
-        <v>0.4R</v>
+        <v>1R</v>
       </c>
       <c r="C52" s="82" t="s">
         <v>87</v>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="B53" s="86">
         <f>IF(B19="Long",ROUND((B45-B43)*B42,0),ROUND((B45-B43)*B42,0))</f>
-        <v>-11223</v>
+        <v>17500</v>
       </c>
       <c r="C53" s="82" t="s">
         <v>89</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B54" s="88" t="str">
         <f>ROUND(B53/B15,1) &amp; "R"</f>
-        <v>-0.7R</v>
+        <v>1.8R</v>
       </c>
       <c r="C54" s="89" t="s">
         <v>91</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B55" s="90">
         <f>IF(B18="Long",(B47-B43)*B42,(B43-B47)*B42)</f>
-        <v>49342.5</v>
+        <v>40000</v>
       </c>
       <c r="C55" s="91" t="s">
         <v>93</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B56" s="92" t="str">
         <f>ROUND(B55/B15,1) &amp; "R"</f>
-        <v>3.3R</v>
+        <v>4R</v>
       </c>
       <c r="C56" s="89" t="s">
         <v>95</v>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B57" s="90">
         <f>IF(B18="Long",(B47-B43)*B49+(B48-B43)*B50,(B43-B47)*B49+(B43-B48)*B50)</f>
-        <v>71540.25</v>
+        <v>58000</v>
       </c>
       <c r="C57" s="89" t="s">
         <v>97</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="B58" s="94" t="str">
         <f>ROUND(B57/B15,1) &amp; "R"</f>
-        <v>4.8R</v>
+        <v>5.8R</v>
       </c>
       <c r="C58" s="95" t="s">
         <v>99</v>

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -38,14 +38,14 @@
 🔵 Blue – BUY</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B47">
+    <comment authorId="0" ref="B55">
       <text>
         <t xml:space="preserve">Legend
 🟠 Orange – SELL
 🔵 Blue – BUY</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B46">
+    <comment authorId="0" ref="B54">
       <text>
         <t xml:space="preserve">Legend
 🟠 Orange – SELL
@@ -78,12 +78,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="122">
+  <si>
+    <t>📊  Position Size Calculator ( Fill in the required fields marked with * )</t>
+  </si>
   <si>
     <t>Symbol</t>
-  </si>
-  <si>
-    <t>📊  Position Size Calculator ( Fill in the required fields marked with * )</t>
   </si>
   <si>
     <t>ACCOUNT SETTINGS</t>
@@ -95,7 +95,13 @@
     <t>Value</t>
   </si>
   <si>
+    <t>Auto fetched from position calculator</t>
+  </si>
+  <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Trade Type</t>
   </si>
   <si>
     <t>*  Trading Capital (₹)</t>
@@ -104,31 +110,31 @@
     <t>Total account equity</t>
   </si>
   <si>
+    <t>Planned Exit Price</t>
+  </si>
+  <si>
+    <t>Must be entered manually</t>
+  </si>
+  <si>
     <t>Max Risk Per Trade (%)</t>
   </si>
   <si>
-    <t>Auto fetched from position calculator</t>
+    <t>Exit Trigger Price</t>
   </si>
   <si>
-    <t>Trade Type</t>
+    <t>Auto calculated</t>
   </si>
   <si>
-    <t>Planned Exit Price</t>
+    <t>Exit Price</t>
   </si>
   <si>
-    <t>% of capital at risk (default: 2% SHORT, 3% LONG)</t>
+    <t>% of capital at risk (default: 2.5% SHORT, 3% LONG)</t>
   </si>
   <si>
     <t>Intraday Leverage Multiplier</t>
   </si>
   <si>
-    <t>Must be entered manually</t>
-  </si>
-  <si>
     <t>Maximum leverage: 4.75x (95% of buying power). Never deploy 100% of buying power. The buffer is not idle money — it is your right to modify orders freely.</t>
-  </si>
-  <si>
-    <t>Exit Trigger Price</t>
   </si>
   <si>
     <t>ATR Risk Multiplier</t>
@@ -138,12 +144,6 @@
   </si>
   <si>
     <t>Fixed Target Multiplier</t>
-  </si>
-  <si>
-    <t>Auto calculated</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
   </si>
   <si>
     <t>Partial Target Multiplier</t>
@@ -210,25 +210,48 @@
     <t>*  Symbol</t>
   </si>
   <si>
-    <t>TRANSRAILL</t>
-  </si>
-  <si>
     <t>Stock Name: Enter the stock name (not case-sensitive). It will be converted to UPPERCASE automatically.</t>
   </si>
   <si>
-    <t>*  Trade Type</t>
+    <t>*  Entry Candle High</t>
   </si>
   <si>
-    <t>Short</t>
+    <t>Mandatory Input Field. Enter high of entry candle</t>
   </si>
   <si>
-    <t>Trade Direction: Select LONG or SHORT. SL and target prices are computed accordingly.</t>
+    <t>*  Entry Candle Low</t>
+  </si>
+  <si>
+    <t>Mandatory Input Field. Enter low of entry candle</t>
+  </si>
+  <si>
+    <t>*  ATR</t>
+  </si>
+  <si>
+    <t>ATR of breakout candle. Must be entered manually</t>
+  </si>
+  <si>
+    <t>*  Spread</t>
+  </si>
+  <si>
+    <t>* Upper Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper Circuit — Trading near this level carries higher risk.
+</t>
+  </si>
+  <si>
+    <t>* Lower Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower Circuit — Trading near this level carries higher risk.
+</t>
   </si>
   <si>
     <t>*  Setup</t>
   </si>
   <si>
-    <t>BTR</t>
+    <t>EVB</t>
   </si>
   <si>
     <t xml:space="preserve">Select Setup: Different setups use different target values based on backtesting.
@@ -238,20 +261,13 @@
 </t>
   </si>
   <si>
-    <t>Mandatory Input Field. Enter high/low of entry candle</t>
+    <t>*  Trade Type</t>
   </si>
   <si>
-    <t>*  ATR</t>
+    <t>Long</t>
   </si>
   <si>
-    <t>ATR of breakout candle or confirmation candle which ever is high. Must be entered manually</t>
-  </si>
-  <si>
-    <t>*  Spread</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper/Lower Circuit — Trading near these levels carries higher risk.
-</t>
+    <t>Trade Direction: Select LONG or SHORT. SL and target prices are computed accordingly.</t>
   </si>
   <si>
     <t>* Order Type</t>
@@ -573,9 +589,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$₹]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="[$₹]#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -620,6 +637,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FF990000"/>
@@ -637,27 +660,21 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -744,14 +761,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF1F3864"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -806,14 +823,6 @@
   <borders count="46">
     <border/>
     <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -821,6 +830,14 @@
         <color rgb="FFCCCCCC"/>
       </top>
       <bottom/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
     </border>
     <border>
       <top style="thin">
@@ -858,6 +875,11 @@
       </right>
     </border>
     <border>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -883,11 +905,6 @@
       </bottom>
     </border>
     <border>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -904,6 +921,27 @@
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -950,14 +988,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
@@ -977,25 +1007,12 @@
       </bottom>
     </border>
     <border>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
-    </border>
-    <border>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -1024,16 +1041,25 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
         <color rgb="FFCCCCCC"/>
       </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
       <bottom/>
     </border>
     <border>
@@ -1043,7 +1069,6 @@
       <right style="thin">
         <color rgb="FFCCCCCC"/>
       </right>
-      <bottom/>
     </border>
     <border>
       <left style="medium">
@@ -1186,14 +1211,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="135">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1213,124 +1238,124 @@
     <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="5" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="10" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="5" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="6" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="6" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="6" fontId="13" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="10" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="12" numFmtId="4" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="14" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="17" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="6" fontId="14" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="14" numFmtId="4" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="6" fontId="13" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="6" fontId="14" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="18" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="6" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="6" fontId="14" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="20" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="21" fillId="6" fontId="14" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="21" fillId="6" fontId="14" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="24" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="6" fontId="13" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="25" fillId="6" fontId="14" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="21" fillId="6" fontId="14" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="6" fontId="13" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="2" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="26" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="24" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="6" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="6" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="26" fillId="6" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="26" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="6" fontId="13" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="26" fillId="6" fontId="14" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="26" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="26" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1356,98 +1381,119 @@
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="18" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="6" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="6" fontId="16" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="21" fillId="6" fontId="16" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="22" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="26" fillId="6" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="6" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="26" fillId="6" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="27" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="28" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="8" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="21" fillId="8" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="29" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="29" fillId="8" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="29" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="29" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="26" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="30" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="8" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="8" fontId="10" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="8" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="26" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="8" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="31" fillId="8" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="31" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="30" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="31" fillId="8" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="31" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="5" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="8" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="8" fontId="9" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="9" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="9" fontId="10" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="9" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="9" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="9" fontId="9" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="9" fontId="10" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="6" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="6" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="6" fontId="11" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="6" fontId="13" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="6" fontId="11" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="6" fontId="13" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="13" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="11" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="7" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1472,13 +1518,13 @@
     <xf borderId="38" fillId="11" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="11" fontId="9" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="11" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="37" fillId="6" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="11" fontId="23" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="11" fontId="23" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="37" fillId="6" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1487,22 +1533,22 @@
     <xf borderId="38" fillId="11" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="7" fontId="25" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="7" fontId="25" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="11" fontId="25" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="11" fontId="25" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="11" fontId="26" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="11" fontId="26" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="11" fontId="26" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="11" fontId="26" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="39" fillId="11" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="11" fontId="27" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="11" fontId="27" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="40" fillId="11" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1535,19 +1581,19 @@
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="31" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1557,7 +1603,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -1616,6 +1662,30 @@
       </fill>
       <border/>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF38761D"/>
+          <bgColor rgb="FF38761D"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF990000"/>
+          <bgColor rgb="FF990000"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
   </dxfs>
 </styleSheet>
 </file>
@@ -1626,7 +1696,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1619250" cy="666750"/>
@@ -1863,8 +1933,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="35.29"/>
-    <col customWidth="1" min="2" max="2" width="26.71"/>
-    <col customWidth="1" min="3" max="3" width="121.14"/>
+    <col customWidth="1" min="2" max="2" width="34.14"/>
+    <col customWidth="1" hidden="1" min="3" max="3" width="121.14"/>
     <col customWidth="1" min="4" max="5" width="8.71"/>
     <col customWidth="1" min="6" max="6" width="16.14"/>
     <col customWidth="1" min="7" max="23" width="8.71"/>
@@ -1872,7 +1942,7 @@
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1934,11 +2004,11 @@
       <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>5</v>
+      <c r="C3" s="14" t="s">
+        <v>6</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1965,14 +2035,14 @@
       <c r="Z3" s="9"/>
     </row>
     <row r="4" ht="32.25" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>6</v>
+      <c r="A4" s="16" t="s">
+        <v>8</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="18">
         <v>400000.0</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>7</v>
+      <c r="C4" s="21" t="s">
+        <v>9</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -1999,15 +2069,15 @@
       <c r="Z4" s="9"/>
     </row>
     <row r="5" ht="21.75" hidden="1" customHeight="1">
-      <c r="A5" s="16" t="s">
-        <v>8</v>
+      <c r="A5" s="24" t="s">
+        <v>12</v>
       </c>
-      <c r="B5" s="22">
-        <f>IF(B21="Short",0.02,0.03)</f>
-        <v>0.02</v>
+      <c r="B5" s="29">
+        <f>IF(B28="Short",0.025,0.03)</f>
+        <v>0.03</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>12</v>
+      <c r="C5" s="30" t="s">
+        <v>16</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -2034,14 +2104,14 @@
       <c r="Z5" s="9"/>
     </row>
     <row r="6" ht="30.0" hidden="1" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>13</v>
+      <c r="A6" s="24" t="s">
+        <v>17</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="31">
         <v>4.75</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>15</v>
+      <c r="C6" s="21" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -2068,14 +2138,14 @@
       <c r="Z6" s="9"/>
     </row>
     <row r="7" ht="21.75" hidden="1" customHeight="1">
-      <c r="A7" s="28" t="s">
-        <v>17</v>
+      <c r="A7" s="32" t="s">
+        <v>19</v>
       </c>
-      <c r="B7" s="29">
-        <v>0.5</v>
+      <c r="B7" s="33">
+        <v>0.55</v>
       </c>
-      <c r="C7" s="30" t="s">
-        <v>18</v>
+      <c r="C7" s="34" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -2102,92 +2172,92 @@
       <c r="Z7" s="9"/>
     </row>
     <row r="8" ht="21.75" hidden="1" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>19</v>
+      <c r="A8" s="35" t="s">
+        <v>21</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="36">
         <f>IF(
-  B21="Long",
+  B28="Long",
   IFS(
-    B22="NSE Topers",8,
-    B22="EVB",6
+    B27="NSE Topers",8,
+    B27="EVB",6
   ),
   6
 )
 +IF(
-  AND(B28="Strong",B21="Long"),
+  AND(B30="Strong",B28="Long"),
   4,
   0
 )</f>
         <v>6</v>
       </c>
-      <c r="C8" s="35" t="str">
+      <c r="C8" s="37" t="str">
         <f>round(B8, 2) &amp; "R"</f>
         <v>6R</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="37"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="39"/>
     </row>
     <row r="9" ht="21.75" hidden="1" customHeight="1">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="40">
         <f>CEILING(B8*2,1)
  </f>
         <v>12</v>
       </c>
-      <c r="C9" s="35" t="str">
+      <c r="C9" s="37" t="str">
         <f>B9 &amp; "R"</f>
         <v>12R</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="37"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="39"/>
     </row>
     <row r="10" ht="21.75" hidden="1" customHeight="1">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="41" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="42">
@@ -2221,45 +2291,45 @@
       <c r="Z10" s="5"/>
     </row>
     <row r="11" ht="21.75" hidden="1" customHeight="1">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="35" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="44">
         <v>0.5</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="37"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="39"/>
     </row>
     <row r="12" ht="21.75" hidden="1" customHeight="1">
       <c r="A12" s="45" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="46">
-        <v>2.1</v>
+        <v>2.0</v>
       </c>
       <c r="C12" s="47" t="s">
         <v>28</v>
@@ -2391,47 +2461,47 @@
       <c r="Z15" s="58"/>
     </row>
     <row r="16" ht="21.75" hidden="1" customHeight="1">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="38">
-        <f>IFERROR(IF(B27="Limit",MAX(1,ROUND(B14*B33/B30,0)),3),0)</f>
-        <v>3</v>
+      <c r="B16" s="40">
+        <f>IFERROR(IF(B29="Limit",MAX(1,ROUND(B14*B35/B32,0)),3),0)</f>
+        <v>0</v>
       </c>
       <c r="C16" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="37"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="39"/>
     </row>
     <row r="17" ht="21.75" hidden="1" customHeight="1">
       <c r="A17" s="60" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="61">
-        <f>IFERROR(IF(B27="Limit",MAX(1,ROUND(B15*B33/B30,0)),3),0)</f>
-        <v>8</v>
+        <f>IFERROR(IF(B29="Limit",MAX(1,ROUND(B15*B35/B32,0)),3),0)</f>
+        <v>0</v>
       </c>
       <c r="C17" s="62" t="s">
         <v>38</v>
@@ -2466,7 +2536,7 @@
       </c>
       <c r="B18" s="66">
         <f>B4*B5</f>
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="C18" s="49" t="s">
         <v>40</v>
@@ -2529,79 +2599,73 @@
       <c r="A20" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="70"/>
+      <c r="C20" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="39"/>
+    </row>
+    <row r="21" ht="46.5" customHeight="1">
+      <c r="A21" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="36"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="37"/>
-    </row>
-    <row r="21" ht="46.5" customHeight="1">
-      <c r="A21" s="69" t="s">
+      <c r="B21" s="72"/>
+      <c r="C21" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="70" t="s">
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="74"/>
+      <c r="P21" s="74"/>
+      <c r="Q21" s="74"/>
+      <c r="R21" s="74"/>
+      <c r="S21" s="74"/>
+      <c r="T21" s="74"/>
+      <c r="U21" s="74"/>
+      <c r="V21" s="74"/>
+      <c r="W21" s="74"/>
+      <c r="X21" s="74"/>
+      <c r="Y21" s="74"/>
+      <c r="Z21" s="75"/>
+    </row>
+    <row r="22" ht="45.0" customHeight="1">
+      <c r="A22" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="B22" s="72"/>
+      <c r="C22" s="77" t="s">
         <v>47</v>
-      </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="36"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="36"/>
-      <c r="Z21" s="37"/>
-    </row>
-    <row r="22" ht="46.5" customHeight="1">
-      <c r="A22" s="71" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="73" t="s">
-        <v>50</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -2627,16 +2691,13 @@
       <c r="Y22" s="8"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" ht="46.5" customHeight="1">
-      <c r="A23" s="74" t="str">
-        <f>IF(B21="Long", "*  Entry Candle High", "*  Entry Candle Low")</f>
-        <v>*  Entry Candle Low</v>
+    <row r="23" ht="45.75" customHeight="1">
+      <c r="A23" s="78" t="s">
+        <v>48</v>
       </c>
-      <c r="B23" s="75">
-        <v>474.3</v>
-      </c>
-      <c r="C23" s="76" t="s">
-        <v>51</v>
+      <c r="B23" s="79"/>
+      <c r="C23" s="30" t="s">
+        <v>49</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -2662,16 +2723,12 @@
       <c r="Y23" s="8"/>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" ht="36.75" customHeight="1">
-      <c r="A24" s="77" t="s">
-        <v>52</v>
+    <row r="24" ht="52.5" customHeight="1">
+      <c r="A24" s="78" t="s">
+        <v>50</v>
       </c>
-      <c r="B24" s="78">
-        <v>4.38</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>53</v>
-      </c>
+      <c r="B24" s="80"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
@@ -2697,13 +2754,13 @@
       <c r="Z24" s="9"/>
     </row>
     <row r="25" ht="52.5" customHeight="1">
-      <c r="A25" s="77" t="s">
-        <v>54</v>
+      <c r="A25" s="81" t="s">
+        <v>51</v>
       </c>
-      <c r="B25" s="79">
-        <v>0.25</v>
+      <c r="B25" s="82"/>
+      <c r="C25" s="83" t="s">
+        <v>52</v>
       </c>
-      <c r="C25" s="15"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -2728,16 +2785,13 @@
       <c r="Y25" s="8"/>
       <c r="Z25" s="9"/>
     </row>
-    <row r="26" ht="52.5" customHeight="1">
-      <c r="A26" s="77" t="str">
-        <f>IF(B21="Long","* Upper Circuit","* Lower Circuit")</f>
-        <v>* Lower Circuit</v>
+    <row r="26" ht="46.5" customHeight="1">
+      <c r="A26" s="81" t="s">
+        <v>53</v>
       </c>
-      <c r="B26" s="79">
-        <v>360.6</v>
-      </c>
-      <c r="C26" s="80" t="s">
-        <v>55</v>
+      <c r="B26" s="82"/>
+      <c r="C26" s="83" t="s">
+        <v>54</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -2764,14 +2818,14 @@
       <c r="Z26" s="9"/>
     </row>
     <row r="27" ht="46.5" customHeight="1">
-      <c r="A27" s="77" t="s">
+      <c r="A27" s="84" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="81" t="s">
+      <c r="C27" s="86" t="s">
         <v>57</v>
-      </c>
-      <c r="C27" s="82" t="s">
-        <v>58</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -2797,49 +2851,50 @@
       <c r="Y27" s="8"/>
       <c r="Z27" s="9"/>
     </row>
-    <row r="28" ht="93.0" customHeight="1">
-      <c r="A28" s="77" t="s">
+    <row r="28" ht="46.5" customHeight="1">
+      <c r="A28" s="69" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="81" t="s">
+      <c r="C28" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="82" t="s">
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="38"/>
+      <c r="Z28" s="39"/>
+    </row>
+    <row r="29" ht="46.5" customHeight="1">
+      <c r="A29" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="8"/>
-      <c r="Z28" s="9"/>
-    </row>
-    <row r="29" ht="46.5" hidden="1" customHeight="1">
-      <c r="A29" s="83" t="s">
+      <c r="B29" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="84">
-        <f>IF(AND(B24&gt;0, B25&gt;0), B25/B24,0)</f>
-        <v>0.05707762557</v>
+      <c r="C29" s="88" t="s">
+        <v>63</v>
       </c>
-      <c r="C29" s="15"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -2864,21 +2919,15 @@
       <c r="Y29" s="8"/>
       <c r="Z29" s="9"/>
     </row>
-    <row r="30" ht="46.5" hidden="1" customHeight="1">
-      <c r="A30" s="83" t="s">
-        <v>63</v>
+    <row r="30" ht="66.0" customHeight="1">
+      <c r="A30" s="78" t="s">
+        <v>64</v>
       </c>
-      <c r="B30" s="85">
-        <f>IF(B23&lt;1,0,
- IF(B23&lt;250,0.01,
- IF(B23&lt;=1000,0.05,
- IF(B23&lt;=5000,0.1,
- IF(B23&lt;=10000,0.5,
- IF(B23&lt;=20000,1,5))))))</f>
-        <v>0.05</v>
+      <c r="B30" s="87" t="s">
+        <v>65</v>
       </c>
-      <c r="C30" s="24" t="s">
-        <v>64</v>
+      <c r="C30" s="88" t="s">
+        <v>66</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -2905,14 +2954,14 @@
       <c r="Z30" s="9"/>
     </row>
     <row r="31" ht="46.5" hidden="1" customHeight="1">
-      <c r="A31" s="83" t="s">
-        <v>65</v>
+      <c r="A31" s="89" t="s">
+        <v>67</v>
       </c>
-      <c r="B31" s="86">
-        <f>IFERROR(IF(B21="Long",B23+B16*B30,B23-B16*B30),0)</f>
-        <v>474.15</v>
+      <c r="B31" s="90">
+        <f>IF(AND(B23&gt;0, B24&gt;0), B24/B23,0)</f>
+        <v>0</v>
       </c>
-      <c r="C31" s="15"/>
+      <c r="C31" s="21"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -2937,12 +2986,22 @@
       <c r="Y31" s="8"/>
       <c r="Z31" s="9"/>
     </row>
-    <row r="32" ht="21.75" hidden="1" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>66</v>
+    <row r="32" ht="46.5" hidden="1" customHeight="1">
+      <c r="A32" s="89" t="s">
+        <v>68</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
+      <c r="B32" s="91">
+        <f>IF(B21&lt;1,0,
+ IF(B21&lt;250,0.01,
+ IF(B21&lt;=1000,0.05,
+ IF(B21&lt;=5000,0.1,
+ IF(B21&lt;=10000,0.5,
+ IF(B21&lt;=20000,1,5))))))</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>69</v>
+      </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
@@ -2967,17 +3026,15 @@
       <c r="Y32" s="8"/>
       <c r="Z32" s="9"/>
     </row>
-    <row r="33" ht="21.75" hidden="1" customHeight="1">
-      <c r="A33" s="16" t="s">
-        <v>67</v>
+    <row r="33" ht="46.5" hidden="1" customHeight="1">
+      <c r="A33" s="89" t="s">
+        <v>70</v>
       </c>
-      <c r="B33" s="87">
-        <f>IF(B30&gt;0,CEILING(B24*B7,B30),0)</f>
-        <v>2.2</v>
+      <c r="B33" s="92">
+        <f>IFERROR(IF(B28="Long",B21+B16*B32,B22-B16*B32),0)</f>
+        <v>0</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>68</v>
-      </c>
+      <c r="C33" s="21"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
@@ -3002,17 +3059,12 @@
       <c r="Y33" s="8"/>
       <c r="Z33" s="9"/>
     </row>
-    <row r="34" ht="33.0" hidden="1" customHeight="1">
-      <c r="A34" s="16" t="s">
-        <v>69</v>
+    <row r="34" ht="21.75" hidden="1" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>71</v>
       </c>
-      <c r="B34" s="87">
-        <f>B4*B5</f>
-        <v>8000</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>70</v>
-      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -3038,15 +3090,15 @@
       <c r="Z34" s="9"/>
     </row>
     <row r="35" ht="21.75" hidden="1" customHeight="1">
-      <c r="A35" s="16" t="s">
-        <v>71</v>
+      <c r="A35" s="24" t="s">
+        <v>72</v>
       </c>
-      <c r="B35" s="87">
-        <f>B4*B6</f>
-        <v>1900000</v>
+      <c r="B35" s="93">
+        <f>IF(B32&gt;0,CEILING(B23*B7,B32),0)</f>
+        <v>0</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>72</v>
+      <c r="C35" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -3072,16 +3124,16 @@
       <c r="Y35" s="8"/>
       <c r="Z35" s="9"/>
     </row>
-    <row r="36" ht="21.75" hidden="1" customHeight="1">
-      <c r="A36" s="16" t="s">
-        <v>73</v>
+    <row r="36" ht="33.0" hidden="1" customHeight="1">
+      <c r="A36" s="24" t="s">
+        <v>74</v>
       </c>
-      <c r="B36" s="88">
-        <f>IF(B33&gt;0,B34/(B33),0)</f>
-        <v>3636.363636</v>
+      <c r="B36" s="93">
+        <f>B4*B5</f>
+        <v>12000</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>74</v>
+      <c r="C36" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -3108,15 +3160,15 @@
       <c r="Z36" s="9"/>
     </row>
     <row r="37" ht="21.75" hidden="1" customHeight="1">
-      <c r="A37" s="16" t="s">
-        <v>75</v>
+      <c r="A37" s="24" t="s">
+        <v>76</v>
       </c>
-      <c r="B37" s="88">
-        <f>IF(B31&gt;0, B35/B31, 0)</f>
-        <v>4007.170727</v>
+      <c r="B37" s="93">
+        <f>B4*B6</f>
+        <v>1900000</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>76</v>
+      <c r="C37" s="21" t="s">
+        <v>77</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -3143,15 +3195,15 @@
       <c r="Z37" s="9"/>
     </row>
     <row r="38" ht="21.75" hidden="1" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>77</v>
+      <c r="A38" s="24" t="s">
+        <v>78</v>
       </c>
-      <c r="B38" s="89">
-        <f>MIN(B36,B37)</f>
-        <v>3636.363636</v>
+      <c r="B38" s="94">
+        <f>IF(B35&gt;0,B36/(B35),0)</f>
+        <v>0</v>
       </c>
-      <c r="C38" s="30" t="s">
-        <v>78</v>
+      <c r="C38" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -3178,14 +3230,16 @@
       <c r="Z38" s="9"/>
     </row>
     <row r="39" ht="21.75" hidden="1" customHeight="1">
-      <c r="A39" s="90" t="s">
-        <v>79</v>
+      <c r="A39" s="24" t="s">
+        <v>80</v>
       </c>
-      <c r="B39" s="91" t="b">
-        <f>B29&gt;B10</f>
+      <c r="B39" s="94">
+        <f>IF(B33&gt;0, B37/B33, 0)</f>
         <v>0</v>
       </c>
-      <c r="C39" s="80"/>
+      <c r="C39" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -3211,14 +3265,16 @@
       <c r="Z39" s="9"/>
     </row>
     <row r="40" ht="21.75" hidden="1" customHeight="1">
-      <c r="A40" s="90" t="s">
-        <v>80</v>
+      <c r="A40" s="32" t="s">
+        <v>82</v>
       </c>
-      <c r="B40" s="91" t="b">
-        <f>IF(B26&lt;1,FALSE,IF(B21="Long",(B26-B52)/B26&lt;=B13,(B52-B26)/B26&lt;=B13))</f>
+      <c r="B40" s="95">
+        <f>MIN(B38,B39)</f>
         <v>0</v>
       </c>
-      <c r="C40" s="80"/>
+      <c r="C40" s="34" t="s">
+        <v>83</v>
+      </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -3244,14 +3300,14 @@
       <c r="Z40" s="9"/>
     </row>
     <row r="41" ht="21.75" hidden="1" customHeight="1">
-      <c r="A41" s="90" t="s">
-        <v>81</v>
+      <c r="A41" s="96" t="s">
+        <v>84</v>
       </c>
-      <c r="B41" s="91" t="b">
-        <f>IF(B26&lt;1,FALSE,IF(B21="Long",(B26-B53)/B26&lt;=B13,(B53-B26)/B26&lt;=B13))</f>
+      <c r="B41" s="97" t="b">
+        <f>B31&gt;B10</f>
         <v>0</v>
       </c>
-      <c r="C41" s="80"/>
+      <c r="C41" s="98"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -3276,28 +3332,19 @@
       <c r="Y41" s="8"/>
       <c r="Z41" s="9"/>
     </row>
-    <row r="42" ht="63.0" customHeight="1">
-      <c r="A42" s="92" t="str">
-        <f>IFERROR(
-   IF(B39,
-      "☠️ Spread Too High — High Slippage Risk - DO NOT TRADE",
-      IF(B40,
-         "☠️ T1 near circuit limit — False Breakout / Reversal Risk - DO NOT TRADE",
-         IF(B41,
-            "☠️ T2 near circuit limit — Exit 100% at T1",
-            ""
-         )
-      )
-   ),
-   ""
-)
-</f>
-        <v/>
+    <row r="42" ht="21.75" hidden="1" customHeight="1">
+      <c r="A42" s="96" t="s">
+        <v>85</v>
       </c>
+      <c r="B42" s="97" t="b">
+        <f>IFERROR(IF(B28="Long",(B25-B54)/B25&lt;=B13,(B54-B26)/B26&lt;=B13), FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="98"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
-      <c r="G42" s="93"/>
+      <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
@@ -3318,12 +3365,15 @@
       <c r="Y42" s="8"/>
       <c r="Z42" s="9"/>
     </row>
-    <row r="43" ht="40.5" customHeight="1">
-      <c r="A43" s="94" t="s">
-        <v>82</v>
+    <row r="43" ht="21.75" hidden="1" customHeight="1">
+      <c r="A43" s="96" t="s">
+        <v>86</v>
       </c>
-      <c r="B43" s="95"/>
-      <c r="C43" s="96"/>
+      <c r="B43" s="97" t="b">
+        <f>IFERROR(IF(B28="Long",(B25-B55)/B25&lt;=B13,(B55-B26)/B26&lt;=B13), FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C43" s="98"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -3348,19 +3398,28 @@
       <c r="Y43" s="8"/>
       <c r="Z43" s="9"/>
     </row>
-    <row r="44" ht="30.75" customHeight="1">
-      <c r="A44" s="97" t="s">
-        <v>0</v>
+    <row r="44" ht="63.0" customHeight="1">
+      <c r="A44" s="99" t="str">
+        <f>IFERROR(
+   IF(B41,
+      "☠️ Spread Too High — High Slippage Risk - DO NOT TRADE",
+      IF(B42,
+         "☠️ T1 near circuit limit — False Breakout / Reversal Risk - DO NOT TRADE",
+         IF(B43,
+            "☠️ T2 near circuit limit — Exit 100% at T1",
+            ""
+         )
+      )
+   ),
+   ""
+)
+</f>
+        <v/>
       </c>
-      <c r="B44" s="98" t="str">
-        <f>B20</f>
-        <v>TRANSRAILL</v>
-      </c>
-      <c r="C44" s="99"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="G44" s="100"/>
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
@@ -3381,17 +3440,12 @@
       <c r="Y44" s="8"/>
       <c r="Z44" s="9"/>
     </row>
-    <row r="45" ht="35.25" customHeight="1">
-      <c r="A45" s="100" t="s">
-        <v>83</v>
+    <row r="45" ht="40.5" customHeight="1">
+      <c r="A45" s="101" t="s">
+        <v>87</v>
       </c>
-      <c r="B45" s="101">
-        <f>IFERROR(IF(OR(B39,B40),0,IF(B38&gt;=5,FLOOR(B38/5,1)*5,FLOOR(B38,1))),0)</f>
-        <v>3635</v>
-      </c>
-      <c r="C45" s="102" t="s">
-        <v>84</v>
-      </c>
+      <c r="B45" s="102"/>
+      <c r="C45" s="103"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -3416,17 +3470,15 @@
       <c r="Y45" s="8"/>
       <c r="Z45" s="9"/>
     </row>
-    <row r="46" ht="41.25" customHeight="1">
-      <c r="A46" s="100" t="s">
-        <v>85</v>
+    <row r="46" ht="30.75" customHeight="1">
+      <c r="A46" s="104" t="s">
+        <v>1</v>
       </c>
-      <c r="B46" s="103">
-        <f>B31</f>
-        <v>474.15</v>
+      <c r="B46" s="105" t="str">
+        <f>B20</f>
+        <v/>
       </c>
-      <c r="C46" s="104" t="s">
-        <v>86</v>
-      </c>
+      <c r="C46" s="106"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -3451,19 +3503,16 @@
       <c r="Y46" s="8"/>
       <c r="Z46" s="9"/>
     </row>
-    <row r="47" ht="43.5" customHeight="1">
-      <c r="A47" s="100" t="str">
-        <f>IF(B27="Limit","Entry Price","")</f>
-        <v>Entry Price</v>
+    <row r="47" ht="35.25" customHeight="1">
+      <c r="A47" s="107" t="s">
+        <v>88</v>
       </c>
-      <c r="B47" s="103">
-        <f>IFERROR(IF(B27="Limit",
-    IF(B21="Long",CEILING(B46+B30*B16,B30),FLOOR(B46-B30*B16,B30)),
-    ""), "")</f>
-        <v>474</v>
+      <c r="B47" s="108">
+        <f>IFERROR(IF(OR(B41,B42),0,IF(B40&gt;=5,FLOOR(B40/5,1)*5,FLOOR(B40,1))),0)</f>
+        <v>0</v>
       </c>
-      <c r="C47" s="104" t="s">
-        <v>87</v>
+      <c r="C47" s="109" t="s">
+        <v>89</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
@@ -3489,26 +3538,16 @@
       <c r="Y47" s="8"/>
       <c r="Z47" s="9"/>
     </row>
-    <row r="48" ht="43.5" customHeight="1">
-      <c r="A48" s="100" t="s">
-        <v>88</v>
+    <row r="48" ht="41.25" customHeight="1">
+      <c r="A48" s="107" t="s">
+        <v>90</v>
       </c>
-      <c r="B48" s="103">
-        <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46),
-  IF(
-    ISNUMBER(entryPrice),
-    IF(B21="Long",
-      FLOOR(entryPrice-B12*B33,B30),
-      CEILING(entryPrice+B12*B33,B30)
-    ),
-    "⚠️ N/A"
-  )
-)</f>
-        <v>478.65</v>
+      <c r="B48" s="110">
+        <f>B33</f>
+        <v>0</v>
       </c>
-      <c r="C48" s="104" t="s">
-        <v>89</v>
+      <c r="C48" s="111" t="s">
+        <v>91</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
@@ -3535,60 +3574,63 @@
       <c r="Z48" s="9"/>
     </row>
     <row r="49" ht="43.5" customHeight="1">
-      <c r="A49" s="105" t="str">
-        <f>IF(B27="Limit","Emergency Exit Price","")</f>
-        <v>Emergency Exit Price</v>
+      <c r="A49" s="107" t="str">
+        <f>IF(B29="Limit","Entry Price","")</f>
+        <v>Entry Price</v>
       </c>
-      <c r="B49" s="106">
-        <f>IFERROR(IF(B27="Limit",
-    IF(B21="Long",FLOOR(B48-B17*B30,B30),CEILING(B48+B17*B30,B30)),
+      <c r="B49" s="110">
+        <f>IFERROR(IF(B29="Limit",
+    IF(B28="Long",CEILING(B48+B32*B16,B32),FLOOR(B48-B32*B16,B32)),
     ""), "")</f>
-        <v>479.05</v>
+        <v>0</v>
       </c>
-      <c r="C49" s="104" t="s">
-        <v>90</v>
+      <c r="C49" s="111" t="s">
+        <v>92</v>
       </c>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="52"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="52"/>
-      <c r="N49" s="52"/>
-      <c r="O49" s="52"/>
-      <c r="P49" s="52"/>
-      <c r="Q49" s="52"/>
-      <c r="R49" s="52"/>
-      <c r="S49" s="52"/>
-      <c r="T49" s="52"/>
-      <c r="U49" s="52"/>
-      <c r="V49" s="52"/>
-      <c r="W49" s="52"/>
-      <c r="X49" s="52"/>
-      <c r="Y49" s="52"/>
-      <c r="Z49" s="53"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
+      <c r="Q49" s="8"/>
+      <c r="R49" s="8"/>
+      <c r="S49" s="8"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="8"/>
+      <c r="V49" s="8"/>
+      <c r="W49" s="8"/>
+      <c r="X49" s="8"/>
+      <c r="Y49" s="8"/>
+      <c r="Z49" s="9"/>
     </row>
     <row r="50" ht="43.5" customHeight="1">
-      <c r="A50" s="100" t="s">
-        <v>16</v>
+      <c r="A50" s="107" t="s">
+        <v>93</v>
       </c>
-      <c r="B50" s="103">
+      <c r="B50" s="110">
         <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46),
+  entryPrice, IF(B29="Limit", B49, B48),
   IF(
-    B21="Long",
-    FLOOR(entryPrice-B33,B30),
-    CEILING(entryPrice+B33,B30)
+    ISNUMBER(entryPrice),
+    IF(B28="Long",
+      FLOOR(entryPrice-B12*B35,B32),
+      CEILING(entryPrice+B12*B35,B32)
+    ),
+    "⚠️ N/A"
   )
 )</f>
-        <v>476.2</v>
+        <v>0</v>
       </c>
-      <c r="C50" s="104" t="s">
-        <v>91</v>
+      <c r="C50" s="111" t="s">
+        <v>94</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
@@ -3615,18 +3657,18 @@
       <c r="Z50" s="9"/>
     </row>
     <row r="51" ht="43.5" customHeight="1">
-      <c r="A51" s="105" t="str">
-        <f>IF(B27="Limit","Exit Price","")</f>
-        <v>Exit Price</v>
+      <c r="A51" s="112" t="str">
+        <f>IF(B29="Limit","Emergency Exit Price","")</f>
+        <v>Emergency Exit Price</v>
       </c>
-      <c r="B51" s="107">
-        <f>IFERROR(IF(B27="Limit",
-    IF(B21="Long",FLOOR(B50-B17*B30,B30),CEILING(B50+B17*B30,B30)),
+      <c r="B51" s="113">
+        <f>IFERROR(IF(B29="Limit",
+    IF(B28="Long",FLOOR(B50-B17*B32,B32),CEILING(B50+B17*B32,B32)),
     ""), "")</f>
-        <v>476.6</v>
+        <v>0</v>
       </c>
-      <c r="C51" s="104" t="s">
-        <v>92</v>
+      <c r="C51" s="111" t="s">
+        <v>95</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -3653,23 +3695,22 @@
       <c r="Z51" s="53"/>
     </row>
     <row r="52" ht="43.5" customHeight="1">
-      <c r="A52" s="100" t="s">
-        <v>93</v>
+      <c r="A52" s="107" t="s">
+        <v>13</v>
       </c>
-      <c r="B52" s="103">
+      <c r="B52" s="110">
         <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46), 
-    IF(
-      B21="Long",
-      CEILING(entryPrice+B8*B33,B30*B16),
-      FLOOR(entryPrice-B8*B33,B30*B16)
-    )
+  entryPrice, IF(B29="Limit", B49, B48),
+  IF(
+    B28="Long",
+    FLOOR(entryPrice-B35,B32),
+    CEILING(entryPrice+B35,B32)
   )
-</f>
-        <v>460.8</v>
+)</f>
+        <v>0</v>
       </c>
-      <c r="C52" s="102" t="s">
-        <v>94</v>
+      <c r="C52" s="111" t="s">
+        <v>96</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
@@ -3695,59 +3736,62 @@
       <c r="Y52" s="8"/>
       <c r="Z52" s="9"/>
     </row>
-    <row r="53" ht="51.0" customHeight="1">
-      <c r="A53" s="100" t="s">
-        <v>95</v>
+    <row r="53" ht="43.5" customHeight="1">
+      <c r="A53" s="112" t="str">
+        <f>IF(B29="Limit","Exit Price","")</f>
+        <v>Exit Price</v>
       </c>
-      <c r="B53" s="103">
+      <c r="B53" s="114">
+        <f>IFERROR(IF(B29="Limit",
+    IF(B28="Long",FLOOR(B52-B17*B32,B32),CEILING(B52+B17*B32,B32)),
+    ""), "")</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="111" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="52"/>
+      <c r="K53" s="52"/>
+      <c r="L53" s="52"/>
+      <c r="M53" s="52"/>
+      <c r="N53" s="52"/>
+      <c r="O53" s="52"/>
+      <c r="P53" s="52"/>
+      <c r="Q53" s="52"/>
+      <c r="R53" s="52"/>
+      <c r="S53" s="52"/>
+      <c r="T53" s="52"/>
+      <c r="U53" s="52"/>
+      <c r="V53" s="52"/>
+      <c r="W53" s="52"/>
+      <c r="X53" s="52"/>
+      <c r="Y53" s="52"/>
+      <c r="Z53" s="53"/>
+    </row>
+    <row r="54" ht="43.5" customHeight="1">
+      <c r="A54" s="107" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="110">
         <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46), 
+  entryPrice, IF(B29="Limit", B49, B48), 
     IF(
-      B21="Long",
-      CEILING(entryPrice+B33*B9,B30*B16),
-      FLOOR(entryPrice-B33*B9,B30*B16)
+      B28="Long",
+      CEILING(entryPrice+B8*B35,B32*B16),
+      FLOOR(entryPrice-B8*B35,B32*B16)
     )
   )
 </f>
-        <v>447.6</v>
+        <v>0</v>
       </c>
-      <c r="C53" s="102" t="s">
-        <v>96</v>
-      </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="8"/>
-      <c r="S53" s="8"/>
-      <c r="T53" s="8"/>
-      <c r="U53" s="8"/>
-      <c r="V53" s="8"/>
-      <c r="W53" s="8"/>
-      <c r="X53" s="8"/>
-      <c r="Y53" s="8"/>
-      <c r="Z53" s="9"/>
-    </row>
-    <row r="54" ht="36.0" customHeight="1">
-      <c r="A54" s="100" t="s">
-        <v>97</v>
-      </c>
-      <c r="B54" s="101">
-        <f>IF(OR(B39,B40),0,IF(B41,B45,ROUND(B11*B45,0)))</f>
-        <v>1818</v>
-      </c>
-      <c r="C54" s="102" t="s">
-        <v>98</v>
+      <c r="C54" s="109" t="s">
+        <v>99</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
@@ -3773,16 +3817,24 @@
       <c r="Y54" s="8"/>
       <c r="Z54" s="9"/>
     </row>
-    <row r="55" ht="36.0" customHeight="1">
-      <c r="A55" s="100" t="s">
-        <v>99</v>
+    <row r="55" ht="51.0" customHeight="1">
+      <c r="A55" s="107" t="s">
+        <v>100</v>
       </c>
-      <c r="B55" s="101">
-        <f>IF(OR(B39,B40),0,IF(B41,0,B45-B54))</f>
-        <v>1817</v>
+      <c r="B55" s="110">
+        <f>LET(
+  entryPrice, IF(B29="Limit", B49, B48), 
+    IF(
+      B28="Long",
+      CEILING(entryPrice+B35*B9,B32*B16),
+      FLOOR(entryPrice-B35*B9,B32*B16)
+    )
+  )
+</f>
+        <v>0</v>
       </c>
-      <c r="C55" s="102" t="s">
-        <v>100</v>
+      <c r="C55" s="109" t="s">
+        <v>101</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -3809,18 +3861,15 @@
       <c r="Z55" s="9"/>
     </row>
     <row r="56" ht="36.0" customHeight="1">
-      <c r="A56" s="100" t="s">
-        <v>101</v>
+      <c r="A56" s="107" t="s">
+        <v>102</v>
       </c>
       <c r="B56" s="108">
-        <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46),
-  IF(B21="Long",ROUND((entryPrice-B50)*B45,0),ROUND((B50-entryPrice)*B45,0))
-)</f>
-        <v>7997</v>
+        <f>IF(OR(B41,B42),0,IF(B43,B47,ROUND(B11*B47,0)))</f>
+        <v>0</v>
       </c>
-      <c r="C56" s="104" t="s">
-        <v>102</v>
+      <c r="C56" s="109" t="s">
+        <v>103</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
@@ -3847,19 +3896,19 @@
       <c r="Z56" s="9"/>
     </row>
     <row r="57" ht="36.0" customHeight="1">
-      <c r="A57" s="100" t="s">
-        <v>103</v>
+      <c r="A57" s="107" t="s">
+        <v>104</v>
       </c>
-      <c r="B57" s="109" t="str">
-        <f>IF(B18&gt;0,ROUND(B56/B18,1)&amp;"R","N/A")</f>
-        <v>1R</v>
+      <c r="B57" s="108">
+        <f>IF(OR(B41,B42),0,IF(B43,0,B47-B56))</f>
+        <v>0</v>
       </c>
-      <c r="C57" s="102" t="s">
-        <v>104</v>
+      <c r="C57" s="109" t="s">
+        <v>105</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
-      <c r="F57" s="93"/>
+      <c r="F57" s="8"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -3882,18 +3931,18 @@
       <c r="Z57" s="9"/>
     </row>
     <row r="58" ht="36.0" customHeight="1">
-      <c r="A58" s="110" t="s">
-        <v>105</v>
+      <c r="A58" s="107" t="s">
+        <v>106</v>
       </c>
-      <c r="B58" s="111">
+      <c r="B58" s="115">
         <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46),
-  IF(B21="Long",ROUND((entryPrice-B48)*B45,0),ROUND((B48-entryPrice)*B45,0))
+  entryPrice, IF(B29="Limit", B49, B48),
+  IF(B28="Long",ROUND((entryPrice-B52)*B47,0),ROUND((B52-entryPrice)*B47,0))
 )</f>
-        <v>16903</v>
+        <v>0</v>
       </c>
-      <c r="C58" s="104" t="s">
-        <v>106</v>
+      <c r="C58" s="111" t="s">
+        <v>107</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
@@ -3920,19 +3969,19 @@
       <c r="Z58" s="9"/>
     </row>
     <row r="59" ht="36.0" customHeight="1">
-      <c r="A59" s="112" t="s">
-        <v>107</v>
+      <c r="A59" s="107" t="s">
+        <v>108</v>
       </c>
-      <c r="B59" s="113" t="str">
+      <c r="B59" s="116" t="str">
         <f>IF(B18&gt;0,ROUND(B58/B18,1)&amp;"R","N/A")</f>
-        <v>2.1R</v>
+        <v>0R</v>
       </c>
-      <c r="C59" s="114" t="s">
-        <v>108</v>
+      <c r="C59" s="109" t="s">
+        <v>109</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="F59" s="100"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -3955,18 +4004,18 @@
       <c r="Z59" s="9"/>
     </row>
     <row r="60" ht="36.0" customHeight="1">
-      <c r="A60" s="112" t="s">
-        <v>109</v>
+      <c r="A60" s="117" t="s">
+        <v>110</v>
       </c>
-      <c r="B60" s="115">
+      <c r="B60" s="118">
         <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46),
-  IF(B21="Long",(B52-entryPrice)*B45,(entryPrice-B52)*B45)
+  entryPrice, IF(B29="Limit", B49, B48),
+  IF(B28="Long",ROUND((entryPrice-B50)*B47,0),ROUND((B50-entryPrice)*B47,0))
 )</f>
-        <v>47982</v>
+        <v>0</v>
       </c>
-      <c r="C60" s="116" t="s">
-        <v>110</v>
+      <c r="C60" s="111" t="s">
+        <v>111</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
@@ -3993,15 +4042,15 @@
       <c r="Z60" s="9"/>
     </row>
     <row r="61" ht="36.0" customHeight="1">
-      <c r="A61" s="112" t="s">
-        <v>111</v>
+      <c r="A61" s="119" t="s">
+        <v>112</v>
       </c>
-      <c r="B61" s="117" t="str">
+      <c r="B61" s="120" t="str">
         <f>IF(B18&gt;0,ROUND(B60/B18,1)&amp;"R","N/A")</f>
-        <v>6R</v>
+        <v>0R</v>
       </c>
-      <c r="C61" s="114" t="s">
-        <v>112</v>
+      <c r="C61" s="121" t="s">
+        <v>113</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
@@ -4028,18 +4077,18 @@
       <c r="Z61" s="9"/>
     </row>
     <row r="62" ht="36.0" customHeight="1">
-      <c r="A62" s="112" t="s">
-        <v>113</v>
+      <c r="A62" s="119" t="s">
+        <v>114</v>
       </c>
-      <c r="B62" s="115">
+      <c r="B62" s="122">
         <f>LET(
-  entryPrice, IF(B27="Limit", B47, B46),
-  IF(B21="Long",(B52-entryPrice)*B54+(B53-entryPrice)*B55,(entryPrice-B52)*B54+(entryPrice-B53)*B55)
+  entryPrice, IF(B29="Limit", B49, B48),
+  IF(B28="Long",(B54-entryPrice)*B47,(entryPrice-B54)*B47)
 )</f>
-        <v>71966.4</v>
+        <v>0</v>
       </c>
-      <c r="C62" s="116" t="s">
-        <v>114</v>
+      <c r="C62" s="123" t="s">
+        <v>115</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -4066,15 +4115,15 @@
       <c r="Z62" s="9"/>
     </row>
     <row r="63" ht="36.0" customHeight="1">
-      <c r="A63" s="118" t="s">
-        <v>115</v>
+      <c r="A63" s="119" t="s">
+        <v>116</v>
       </c>
-      <c r="B63" s="119" t="str">
+      <c r="B63" s="124" t="str">
         <f>IF(B18&gt;0,ROUND(B62/B18,1)&amp;"R","N/A")</f>
-        <v>9R</v>
+        <v>0R</v>
       </c>
-      <c r="C63" s="120" t="s">
-        <v>116</v>
+      <c r="C63" s="121" t="s">
+        <v>117</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -4100,10 +4149,20 @@
       <c r="Y63" s="8"/>
       <c r="Z63" s="9"/>
     </row>
-    <row r="64" ht="21.75" customHeight="1">
-      <c r="A64" s="121"/>
-      <c r="B64" s="122"/>
-      <c r="C64" s="123"/>
+    <row r="64" ht="36.0" customHeight="1">
+      <c r="A64" s="119" t="s">
+        <v>118</v>
+      </c>
+      <c r="B64" s="122">
+        <f>LET(
+  entryPrice, IF(B29="Limit", B49, B48),
+  IF(B28="Long",(B54-entryPrice)*B56+(B55-entryPrice)*B57,(entryPrice-B54)*B56+(entryPrice-B55)*B57)
+)</f>
+        <v>0</v>
+      </c>
+      <c r="C64" s="123" t="s">
+        <v>119</v>
+      </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
@@ -4128,10 +4187,17 @@
       <c r="Y64" s="8"/>
       <c r="Z64" s="9"/>
     </row>
-    <row r="65" ht="21.75" customHeight="1">
-      <c r="A65" s="121"/>
-      <c r="B65" s="122"/>
-      <c r="C65" s="123"/>
+    <row r="65" ht="36.0" customHeight="1">
+      <c r="A65" s="125" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" s="126" t="str">
+        <f>IF(B18&gt;0,ROUND(B64/B18,1)&amp;"R","N/A")</f>
+        <v>0R</v>
+      </c>
+      <c r="C65" s="127" t="s">
+        <v>121</v>
+      </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
@@ -4157,9 +4223,9 @@
       <c r="Z65" s="9"/>
     </row>
     <row r="66" ht="21.75" customHeight="1">
-      <c r="A66" s="121"/>
-      <c r="B66" s="122"/>
-      <c r="C66" s="123"/>
+      <c r="A66" s="128"/>
+      <c r="B66" s="129"/>
+      <c r="C66" s="130"/>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
@@ -4184,10 +4250,10 @@
       <c r="Y66" s="8"/>
       <c r="Z66" s="9"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="121"/>
-      <c r="B67" s="122"/>
-      <c r="C67" s="123"/>
+    <row r="67" ht="21.75" customHeight="1">
+      <c r="A67" s="128"/>
+      <c r="B67" s="129"/>
+      <c r="C67" s="130"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
@@ -4212,10 +4278,10 @@
       <c r="Y67" s="8"/>
       <c r="Z67" s="9"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="121"/>
-      <c r="B68" s="122"/>
-      <c r="C68" s="123"/>
+    <row r="68" ht="21.75" customHeight="1">
+      <c r="A68" s="128"/>
+      <c r="B68" s="129"/>
+      <c r="C68" s="130"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
@@ -4241,9 +4307,9 @@
       <c r="Z68" s="9"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="121"/>
-      <c r="B69" s="122"/>
-      <c r="C69" s="123"/>
+      <c r="A69" s="128"/>
+      <c r="B69" s="129"/>
+      <c r="C69" s="130"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
@@ -4269,9 +4335,9 @@
       <c r="Z69" s="9"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="121"/>
-      <c r="B70" s="122"/>
-      <c r="C70" s="123"/>
+      <c r="A70" s="128"/>
+      <c r="B70" s="129"/>
+      <c r="C70" s="130"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
@@ -4297,9 +4363,9 @@
       <c r="Z70" s="9"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="121"/>
-      <c r="B71" s="122"/>
-      <c r="C71" s="123"/>
+      <c r="A71" s="128"/>
+      <c r="B71" s="129"/>
+      <c r="C71" s="130"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
@@ -4325,9 +4391,9 @@
       <c r="Z71" s="9"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="121"/>
-      <c r="B72" s="122"/>
-      <c r="C72" s="123"/>
+      <c r="A72" s="128"/>
+      <c r="B72" s="129"/>
+      <c r="C72" s="130"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
@@ -4353,9 +4419,9 @@
       <c r="Z72" s="9"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="121"/>
-      <c r="B73" s="122"/>
-      <c r="C73" s="123"/>
+      <c r="A73" s="128"/>
+      <c r="B73" s="129"/>
+      <c r="C73" s="130"/>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
@@ -4381,9 +4447,9 @@
       <c r="Z73" s="9"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="121"/>
-      <c r="B74" s="122"/>
-      <c r="C74" s="123"/>
+      <c r="A74" s="128"/>
+      <c r="B74" s="129"/>
+      <c r="C74" s="130"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
@@ -4409,9 +4475,9 @@
       <c r="Z74" s="9"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="121"/>
-      <c r="B75" s="122"/>
-      <c r="C75" s="123"/>
+      <c r="A75" s="128"/>
+      <c r="B75" s="129"/>
+      <c r="C75" s="130"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
@@ -4437,9 +4503,9 @@
       <c r="Z75" s="9"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="121"/>
-      <c r="B76" s="122"/>
-      <c r="C76" s="123"/>
+      <c r="A76" s="128"/>
+      <c r="B76" s="129"/>
+      <c r="C76" s="130"/>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -4465,9 +4531,9 @@
       <c r="Z76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="121"/>
-      <c r="B77" s="122"/>
-      <c r="C77" s="123"/>
+      <c r="A77" s="128"/>
+      <c r="B77" s="129"/>
+      <c r="C77" s="130"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -4493,9 +4559,9 @@
       <c r="Z77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="121"/>
-      <c r="B78" s="122"/>
-      <c r="C78" s="123"/>
+      <c r="A78" s="128"/>
+      <c r="B78" s="129"/>
+      <c r="C78" s="130"/>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -4521,9 +4587,9 @@
       <c r="Z78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="121"/>
-      <c r="B79" s="122"/>
-      <c r="C79" s="123"/>
+      <c r="A79" s="128"/>
+      <c r="B79" s="129"/>
+      <c r="C79" s="130"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
@@ -4549,9 +4615,9 @@
       <c r="Z79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="121"/>
-      <c r="B80" s="122"/>
-      <c r="C80" s="123"/>
+      <c r="A80" s="128"/>
+      <c r="B80" s="129"/>
+      <c r="C80" s="130"/>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
@@ -4577,9 +4643,9 @@
       <c r="Z80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="121"/>
-      <c r="B81" s="122"/>
-      <c r="C81" s="123"/>
+      <c r="A81" s="128"/>
+      <c r="B81" s="129"/>
+      <c r="C81" s="130"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
@@ -4605,9 +4671,9 @@
       <c r="Z81" s="9"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="121"/>
-      <c r="B82" s="122"/>
-      <c r="C82" s="123"/>
+      <c r="A82" s="128"/>
+      <c r="B82" s="129"/>
+      <c r="C82" s="130"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
@@ -4633,9 +4699,9 @@
       <c r="Z82" s="9"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="121"/>
-      <c r="B83" s="122"/>
-      <c r="C83" s="123"/>
+      <c r="A83" s="128"/>
+      <c r="B83" s="129"/>
+      <c r="C83" s="130"/>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
@@ -4661,9 +4727,9 @@
       <c r="Z83" s="9"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="121"/>
-      <c r="B84" s="122"/>
-      <c r="C84" s="123"/>
+      <c r="A84" s="128"/>
+      <c r="B84" s="129"/>
+      <c r="C84" s="130"/>
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
@@ -4689,9 +4755,9 @@
       <c r="Z84" s="9"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="121"/>
-      <c r="B85" s="122"/>
-      <c r="C85" s="123"/>
+      <c r="A85" s="128"/>
+      <c r="B85" s="129"/>
+      <c r="C85" s="130"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
@@ -4717,9 +4783,9 @@
       <c r="Z85" s="9"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="121"/>
-      <c r="B86" s="122"/>
-      <c r="C86" s="123"/>
+      <c r="A86" s="128"/>
+      <c r="B86" s="129"/>
+      <c r="C86" s="130"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
@@ -4745,9 +4811,9 @@
       <c r="Z86" s="9"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="121"/>
-      <c r="B87" s="122"/>
-      <c r="C87" s="123"/>
+      <c r="A87" s="128"/>
+      <c r="B87" s="129"/>
+      <c r="C87" s="130"/>
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
@@ -4773,9 +4839,9 @@
       <c r="Z87" s="9"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="121"/>
-      <c r="B88" s="122"/>
-      <c r="C88" s="123"/>
+      <c r="A88" s="128"/>
+      <c r="B88" s="129"/>
+      <c r="C88" s="130"/>
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
       <c r="F88" s="8"/>
@@ -4801,9 +4867,9 @@
       <c r="Z88" s="9"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="121"/>
-      <c r="B89" s="122"/>
-      <c r="C89" s="123"/>
+      <c r="A89" s="128"/>
+      <c r="B89" s="129"/>
+      <c r="C89" s="130"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
@@ -4829,9 +4895,9 @@
       <c r="Z89" s="9"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="121"/>
-      <c r="B90" s="122"/>
-      <c r="C90" s="123"/>
+      <c r="A90" s="128"/>
+      <c r="B90" s="129"/>
+      <c r="C90" s="130"/>
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
@@ -4857,9 +4923,9 @@
       <c r="Z90" s="9"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="121"/>
-      <c r="B91" s="122"/>
-      <c r="C91" s="123"/>
+      <c r="A91" s="128"/>
+      <c r="B91" s="129"/>
+      <c r="C91" s="130"/>
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
@@ -4885,9 +4951,9 @@
       <c r="Z91" s="9"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="121"/>
-      <c r="B92" s="122"/>
-      <c r="C92" s="123"/>
+      <c r="A92" s="128"/>
+      <c r="B92" s="129"/>
+      <c r="C92" s="130"/>
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
@@ -4913,9 +4979,9 @@
       <c r="Z92" s="9"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="121"/>
-      <c r="B93" s="122"/>
-      <c r="C93" s="123"/>
+      <c r="A93" s="128"/>
+      <c r="B93" s="129"/>
+      <c r="C93" s="130"/>
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
@@ -4941,9 +5007,9 @@
       <c r="Z93" s="9"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="121"/>
-      <c r="B94" s="122"/>
-      <c r="C94" s="123"/>
+      <c r="A94" s="128"/>
+      <c r="B94" s="129"/>
+      <c r="C94" s="130"/>
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
@@ -4969,9 +5035,9 @@
       <c r="Z94" s="9"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="121"/>
-      <c r="B95" s="122"/>
-      <c r="C95" s="123"/>
+      <c r="A95" s="128"/>
+      <c r="B95" s="129"/>
+      <c r="C95" s="130"/>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
@@ -4997,9 +5063,9 @@
       <c r="Z95" s="9"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="121"/>
-      <c r="B96" s="122"/>
-      <c r="C96" s="123"/>
+      <c r="A96" s="128"/>
+      <c r="B96" s="129"/>
+      <c r="C96" s="130"/>
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
@@ -5025,9 +5091,9 @@
       <c r="Z96" s="9"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="121"/>
-      <c r="B97" s="122"/>
-      <c r="C97" s="123"/>
+      <c r="A97" s="128"/>
+      <c r="B97" s="129"/>
+      <c r="C97" s="130"/>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
@@ -5053,9 +5119,9 @@
       <c r="Z97" s="9"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="121"/>
-      <c r="B98" s="122"/>
-      <c r="C98" s="123"/>
+      <c r="A98" s="128"/>
+      <c r="B98" s="129"/>
+      <c r="C98" s="130"/>
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
@@ -5081,9 +5147,9 @@
       <c r="Z98" s="9"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="121"/>
-      <c r="B99" s="122"/>
-      <c r="C99" s="123"/>
+      <c r="A99" s="128"/>
+      <c r="B99" s="129"/>
+      <c r="C99" s="130"/>
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
@@ -5109,9 +5175,9 @@
       <c r="Z99" s="9"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="121"/>
-      <c r="B100" s="122"/>
-      <c r="C100" s="123"/>
+      <c r="A100" s="128"/>
+      <c r="B100" s="129"/>
+      <c r="C100" s="130"/>
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -5137,9 +5203,9 @@
       <c r="Z100" s="9"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="121"/>
-      <c r="B101" s="122"/>
-      <c r="C101" s="123"/>
+      <c r="A101" s="128"/>
+      <c r="B101" s="129"/>
+      <c r="C101" s="130"/>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
@@ -5165,9 +5231,9 @@
       <c r="Z101" s="9"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="121"/>
-      <c r="B102" s="122"/>
-      <c r="C102" s="123"/>
+      <c r="A102" s="128"/>
+      <c r="B102" s="129"/>
+      <c r="C102" s="130"/>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
@@ -5193,9 +5259,9 @@
       <c r="Z102" s="9"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="121"/>
-      <c r="B103" s="122"/>
-      <c r="C103" s="123"/>
+      <c r="A103" s="128"/>
+      <c r="B103" s="129"/>
+      <c r="C103" s="130"/>
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
@@ -5221,9 +5287,9 @@
       <c r="Z103" s="9"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="121"/>
-      <c r="B104" s="122"/>
-      <c r="C104" s="123"/>
+      <c r="A104" s="128"/>
+      <c r="B104" s="129"/>
+      <c r="C104" s="130"/>
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
@@ -5249,9 +5315,9 @@
       <c r="Z104" s="9"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="121"/>
-      <c r="B105" s="122"/>
-      <c r="C105" s="123"/>
+      <c r="A105" s="128"/>
+      <c r="B105" s="129"/>
+      <c r="C105" s="130"/>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
@@ -5277,9 +5343,9 @@
       <c r="Z105" s="9"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="121"/>
-      <c r="B106" s="122"/>
-      <c r="C106" s="123"/>
+      <c r="A106" s="128"/>
+      <c r="B106" s="129"/>
+      <c r="C106" s="130"/>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
@@ -5305,9 +5371,9 @@
       <c r="Z106" s="9"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="121"/>
-      <c r="B107" s="122"/>
-      <c r="C107" s="123"/>
+      <c r="A107" s="128"/>
+      <c r="B107" s="129"/>
+      <c r="C107" s="130"/>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
@@ -5333,9 +5399,9 @@
       <c r="Z107" s="9"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="121"/>
-      <c r="B108" s="122"/>
-      <c r="C108" s="123"/>
+      <c r="A108" s="128"/>
+      <c r="B108" s="129"/>
+      <c r="C108" s="130"/>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
@@ -5361,9 +5427,9 @@
       <c r="Z108" s="9"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="121"/>
-      <c r="B109" s="122"/>
-      <c r="C109" s="123"/>
+      <c r="A109" s="128"/>
+      <c r="B109" s="129"/>
+      <c r="C109" s="130"/>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
@@ -5389,9 +5455,9 @@
       <c r="Z109" s="9"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="121"/>
-      <c r="B110" s="122"/>
-      <c r="C110" s="123"/>
+      <c r="A110" s="128"/>
+      <c r="B110" s="129"/>
+      <c r="C110" s="130"/>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
@@ -5417,9 +5483,9 @@
       <c r="Z110" s="9"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="121"/>
-      <c r="B111" s="122"/>
-      <c r="C111" s="123"/>
+      <c r="A111" s="128"/>
+      <c r="B111" s="129"/>
+      <c r="C111" s="130"/>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
@@ -5445,9 +5511,9 @@
       <c r="Z111" s="9"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="121"/>
-      <c r="B112" s="122"/>
-      <c r="C112" s="123"/>
+      <c r="A112" s="128"/>
+      <c r="B112" s="129"/>
+      <c r="C112" s="130"/>
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
@@ -5473,9 +5539,9 @@
       <c r="Z112" s="9"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="121"/>
-      <c r="B113" s="122"/>
-      <c r="C113" s="123"/>
+      <c r="A113" s="128"/>
+      <c r="B113" s="129"/>
+      <c r="C113" s="130"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
@@ -5501,9 +5567,9 @@
       <c r="Z113" s="9"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="121"/>
-      <c r="B114" s="122"/>
-      <c r="C114" s="123"/>
+      <c r="A114" s="128"/>
+      <c r="B114" s="129"/>
+      <c r="C114" s="130"/>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
@@ -5529,9 +5595,9 @@
       <c r="Z114" s="9"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="121"/>
-      <c r="B115" s="122"/>
-      <c r="C115" s="123"/>
+      <c r="A115" s="128"/>
+      <c r="B115" s="129"/>
+      <c r="C115" s="130"/>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
@@ -5557,9 +5623,9 @@
       <c r="Z115" s="9"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="121"/>
-      <c r="B116" s="122"/>
-      <c r="C116" s="123"/>
+      <c r="A116" s="128"/>
+      <c r="B116" s="129"/>
+      <c r="C116" s="130"/>
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
@@ -5585,9 +5651,9 @@
       <c r="Z116" s="9"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="121"/>
-      <c r="B117" s="122"/>
-      <c r="C117" s="123"/>
+      <c r="A117" s="128"/>
+      <c r="B117" s="129"/>
+      <c r="C117" s="130"/>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
@@ -5613,9 +5679,9 @@
       <c r="Z117" s="9"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="121"/>
-      <c r="B118" s="122"/>
-      <c r="C118" s="123"/>
+      <c r="A118" s="128"/>
+      <c r="B118" s="129"/>
+      <c r="C118" s="130"/>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
@@ -5641,9 +5707,9 @@
       <c r="Z118" s="9"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="121"/>
-      <c r="B119" s="122"/>
-      <c r="C119" s="123"/>
+      <c r="A119" s="128"/>
+      <c r="B119" s="129"/>
+      <c r="C119" s="130"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
@@ -5669,9 +5735,9 @@
       <c r="Z119" s="9"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="121"/>
-      <c r="B120" s="122"/>
-      <c r="C120" s="123"/>
+      <c r="A120" s="128"/>
+      <c r="B120" s="129"/>
+      <c r="C120" s="130"/>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
@@ -5697,9 +5763,9 @@
       <c r="Z120" s="9"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="121"/>
-      <c r="B121" s="122"/>
-      <c r="C121" s="123"/>
+      <c r="A121" s="128"/>
+      <c r="B121" s="129"/>
+      <c r="C121" s="130"/>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
@@ -5725,9 +5791,9 @@
       <c r="Z121" s="9"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="121"/>
-      <c r="B122" s="122"/>
-      <c r="C122" s="123"/>
+      <c r="A122" s="128"/>
+      <c r="B122" s="129"/>
+      <c r="C122" s="130"/>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
@@ -5753,9 +5819,9 @@
       <c r="Z122" s="9"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="121"/>
-      <c r="B123" s="122"/>
-      <c r="C123" s="123"/>
+      <c r="A123" s="128"/>
+      <c r="B123" s="129"/>
+      <c r="C123" s="130"/>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
@@ -5781,9 +5847,9 @@
       <c r="Z123" s="9"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="121"/>
-      <c r="B124" s="122"/>
-      <c r="C124" s="123"/>
+      <c r="A124" s="128"/>
+      <c r="B124" s="129"/>
+      <c r="C124" s="130"/>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
@@ -5809,9 +5875,9 @@
       <c r="Z124" s="9"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="121"/>
-      <c r="B125" s="122"/>
-      <c r="C125" s="123"/>
+      <c r="A125" s="128"/>
+      <c r="B125" s="129"/>
+      <c r="C125" s="130"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
@@ -5837,9 +5903,9 @@
       <c r="Z125" s="9"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="121"/>
-      <c r="B126" s="122"/>
-      <c r="C126" s="123"/>
+      <c r="A126" s="128"/>
+      <c r="B126" s="129"/>
+      <c r="C126" s="130"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
@@ -5865,9 +5931,9 @@
       <c r="Z126" s="9"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="121"/>
-      <c r="B127" s="122"/>
-      <c r="C127" s="123"/>
+      <c r="A127" s="128"/>
+      <c r="B127" s="129"/>
+      <c r="C127" s="130"/>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
@@ -5893,9 +5959,9 @@
       <c r="Z127" s="9"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="121"/>
-      <c r="B128" s="122"/>
-      <c r="C128" s="123"/>
+      <c r="A128" s="128"/>
+      <c r="B128" s="129"/>
+      <c r="C128" s="130"/>
       <c r="D128" s="8"/>
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
@@ -5921,9 +5987,9 @@
       <c r="Z128" s="9"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="121"/>
-      <c r="B129" s="122"/>
-      <c r="C129" s="123"/>
+      <c r="A129" s="128"/>
+      <c r="B129" s="129"/>
+      <c r="C129" s="130"/>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
@@ -5949,9 +6015,9 @@
       <c r="Z129" s="9"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="121"/>
-      <c r="B130" s="122"/>
-      <c r="C130" s="123"/>
+      <c r="A130" s="128"/>
+      <c r="B130" s="129"/>
+      <c r="C130" s="130"/>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
@@ -5977,9 +6043,9 @@
       <c r="Z130" s="9"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="121"/>
-      <c r="B131" s="122"/>
-      <c r="C131" s="123"/>
+      <c r="A131" s="128"/>
+      <c r="B131" s="129"/>
+      <c r="C131" s="130"/>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
@@ -6005,9 +6071,9 @@
       <c r="Z131" s="9"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="121"/>
-      <c r="B132" s="122"/>
-      <c r="C132" s="123"/>
+      <c r="A132" s="128"/>
+      <c r="B132" s="129"/>
+      <c r="C132" s="130"/>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
@@ -6033,9 +6099,9 @@
       <c r="Z132" s="9"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="121"/>
-      <c r="B133" s="122"/>
-      <c r="C133" s="123"/>
+      <c r="A133" s="128"/>
+      <c r="B133" s="129"/>
+      <c r="C133" s="130"/>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
@@ -6061,9 +6127,9 @@
       <c r="Z133" s="9"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="121"/>
-      <c r="B134" s="122"/>
-      <c r="C134" s="123"/>
+      <c r="A134" s="128"/>
+      <c r="B134" s="129"/>
+      <c r="C134" s="130"/>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
@@ -6089,9 +6155,9 @@
       <c r="Z134" s="9"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="121"/>
-      <c r="B135" s="122"/>
-      <c r="C135" s="123"/>
+      <c r="A135" s="128"/>
+      <c r="B135" s="129"/>
+      <c r="C135" s="130"/>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
@@ -6117,9 +6183,9 @@
       <c r="Z135" s="9"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="121"/>
-      <c r="B136" s="122"/>
-      <c r="C136" s="123"/>
+      <c r="A136" s="128"/>
+      <c r="B136" s="129"/>
+      <c r="C136" s="130"/>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
@@ -6145,9 +6211,9 @@
       <c r="Z136" s="9"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="121"/>
-      <c r="B137" s="122"/>
-      <c r="C137" s="123"/>
+      <c r="A137" s="128"/>
+      <c r="B137" s="129"/>
+      <c r="C137" s="130"/>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
@@ -6173,9 +6239,9 @@
       <c r="Z137" s="9"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="121"/>
-      <c r="B138" s="122"/>
-      <c r="C138" s="123"/>
+      <c r="A138" s="128"/>
+      <c r="B138" s="129"/>
+      <c r="C138" s="130"/>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
@@ -6201,9 +6267,9 @@
       <c r="Z138" s="9"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="121"/>
-      <c r="B139" s="122"/>
-      <c r="C139" s="123"/>
+      <c r="A139" s="128"/>
+      <c r="B139" s="129"/>
+      <c r="C139" s="130"/>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
@@ -6229,9 +6295,9 @@
       <c r="Z139" s="9"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="121"/>
-      <c r="B140" s="122"/>
-      <c r="C140" s="123"/>
+      <c r="A140" s="128"/>
+      <c r="B140" s="129"/>
+      <c r="C140" s="130"/>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
@@ -6257,9 +6323,9 @@
       <c r="Z140" s="9"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="121"/>
-      <c r="B141" s="122"/>
-      <c r="C141" s="123"/>
+      <c r="A141" s="128"/>
+      <c r="B141" s="129"/>
+      <c r="C141" s="130"/>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
@@ -6285,9 +6351,9 @@
       <c r="Z141" s="9"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="121"/>
-      <c r="B142" s="122"/>
-      <c r="C142" s="123"/>
+      <c r="A142" s="128"/>
+      <c r="B142" s="129"/>
+      <c r="C142" s="130"/>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
@@ -6313,9 +6379,9 @@
       <c r="Z142" s="9"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="121"/>
-      <c r="B143" s="122"/>
-      <c r="C143" s="123"/>
+      <c r="A143" s="128"/>
+      <c r="B143" s="129"/>
+      <c r="C143" s="130"/>
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
@@ -6341,9 +6407,9 @@
       <c r="Z143" s="9"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="121"/>
-      <c r="B144" s="122"/>
-      <c r="C144" s="123"/>
+      <c r="A144" s="128"/>
+      <c r="B144" s="129"/>
+      <c r="C144" s="130"/>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
@@ -6369,9 +6435,9 @@
       <c r="Z144" s="9"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="121"/>
-      <c r="B145" s="122"/>
-      <c r="C145" s="123"/>
+      <c r="A145" s="128"/>
+      <c r="B145" s="129"/>
+      <c r="C145" s="130"/>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
@@ -6397,9 +6463,9 @@
       <c r="Z145" s="9"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="121"/>
-      <c r="B146" s="122"/>
-      <c r="C146" s="123"/>
+      <c r="A146" s="128"/>
+      <c r="B146" s="129"/>
+      <c r="C146" s="130"/>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
@@ -6425,9 +6491,9 @@
       <c r="Z146" s="9"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="121"/>
-      <c r="B147" s="122"/>
-      <c r="C147" s="123"/>
+      <c r="A147" s="128"/>
+      <c r="B147" s="129"/>
+      <c r="C147" s="130"/>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
@@ -6453,9 +6519,9 @@
       <c r="Z147" s="9"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="121"/>
-      <c r="B148" s="122"/>
-      <c r="C148" s="123"/>
+      <c r="A148" s="128"/>
+      <c r="B148" s="129"/>
+      <c r="C148" s="130"/>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
@@ -6481,9 +6547,9 @@
       <c r="Z148" s="9"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="121"/>
-      <c r="B149" s="122"/>
-      <c r="C149" s="123"/>
+      <c r="A149" s="128"/>
+      <c r="B149" s="129"/>
+      <c r="C149" s="130"/>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
@@ -6509,9 +6575,9 @@
       <c r="Z149" s="9"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="121"/>
-      <c r="B150" s="122"/>
-      <c r="C150" s="123"/>
+      <c r="A150" s="128"/>
+      <c r="B150" s="129"/>
+      <c r="C150" s="130"/>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
@@ -6537,9 +6603,9 @@
       <c r="Z150" s="9"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="121"/>
-      <c r="B151" s="122"/>
-      <c r="C151" s="123"/>
+      <c r="A151" s="128"/>
+      <c r="B151" s="129"/>
+      <c r="C151" s="130"/>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
@@ -6565,9 +6631,9 @@
       <c r="Z151" s="9"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="121"/>
-      <c r="B152" s="122"/>
-      <c r="C152" s="123"/>
+      <c r="A152" s="128"/>
+      <c r="B152" s="129"/>
+      <c r="C152" s="130"/>
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
@@ -6593,9 +6659,9 @@
       <c r="Z152" s="9"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="121"/>
-      <c r="B153" s="122"/>
-      <c r="C153" s="123"/>
+      <c r="A153" s="128"/>
+      <c r="B153" s="129"/>
+      <c r="C153" s="130"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
@@ -6621,9 +6687,9 @@
       <c r="Z153" s="9"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="121"/>
-      <c r="B154" s="122"/>
-      <c r="C154" s="123"/>
+      <c r="A154" s="128"/>
+      <c r="B154" s="129"/>
+      <c r="C154" s="130"/>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
@@ -6649,9 +6715,9 @@
       <c r="Z154" s="9"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="121"/>
-      <c r="B155" s="122"/>
-      <c r="C155" s="123"/>
+      <c r="A155" s="128"/>
+      <c r="B155" s="129"/>
+      <c r="C155" s="130"/>
       <c r="D155" s="8"/>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
@@ -6677,9 +6743,9 @@
       <c r="Z155" s="9"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="121"/>
-      <c r="B156" s="122"/>
-      <c r="C156" s="123"/>
+      <c r="A156" s="128"/>
+      <c r="B156" s="129"/>
+      <c r="C156" s="130"/>
       <c r="D156" s="8"/>
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
@@ -6705,9 +6771,9 @@
       <c r="Z156" s="9"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="121"/>
-      <c r="B157" s="122"/>
-      <c r="C157" s="123"/>
+      <c r="A157" s="128"/>
+      <c r="B157" s="129"/>
+      <c r="C157" s="130"/>
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
@@ -6733,9 +6799,9 @@
       <c r="Z157" s="9"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="121"/>
-      <c r="B158" s="122"/>
-      <c r="C158" s="123"/>
+      <c r="A158" s="128"/>
+      <c r="B158" s="129"/>
+      <c r="C158" s="130"/>
       <c r="D158" s="8"/>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
@@ -6761,9 +6827,9 @@
       <c r="Z158" s="9"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="121"/>
-      <c r="B159" s="122"/>
-      <c r="C159" s="123"/>
+      <c r="A159" s="128"/>
+      <c r="B159" s="129"/>
+      <c r="C159" s="130"/>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
@@ -6789,9 +6855,9 @@
       <c r="Z159" s="9"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="121"/>
-      <c r="B160" s="122"/>
-      <c r="C160" s="123"/>
+      <c r="A160" s="128"/>
+      <c r="B160" s="129"/>
+      <c r="C160" s="130"/>
       <c r="D160" s="8"/>
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
@@ -6817,9 +6883,9 @@
       <c r="Z160" s="9"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="121"/>
-      <c r="B161" s="122"/>
-      <c r="C161" s="123"/>
+      <c r="A161" s="128"/>
+      <c r="B161" s="129"/>
+      <c r="C161" s="130"/>
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
@@ -6845,9 +6911,9 @@
       <c r="Z161" s="9"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="121"/>
-      <c r="B162" s="122"/>
-      <c r="C162" s="123"/>
+      <c r="A162" s="128"/>
+      <c r="B162" s="129"/>
+      <c r="C162" s="130"/>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
@@ -6873,9 +6939,9 @@
       <c r="Z162" s="9"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="121"/>
-      <c r="B163" s="122"/>
-      <c r="C163" s="123"/>
+      <c r="A163" s="128"/>
+      <c r="B163" s="129"/>
+      <c r="C163" s="130"/>
       <c r="D163" s="8"/>
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
@@ -6901,9 +6967,9 @@
       <c r="Z163" s="9"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="121"/>
-      <c r="B164" s="122"/>
-      <c r="C164" s="123"/>
+      <c r="A164" s="128"/>
+      <c r="B164" s="129"/>
+      <c r="C164" s="130"/>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
@@ -6929,9 +6995,9 @@
       <c r="Z164" s="9"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="121"/>
-      <c r="B165" s="122"/>
-      <c r="C165" s="123"/>
+      <c r="A165" s="128"/>
+      <c r="B165" s="129"/>
+      <c r="C165" s="130"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
@@ -6957,9 +7023,9 @@
       <c r="Z165" s="9"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="121"/>
-      <c r="B166" s="122"/>
-      <c r="C166" s="123"/>
+      <c r="A166" s="128"/>
+      <c r="B166" s="129"/>
+      <c r="C166" s="130"/>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
@@ -6985,9 +7051,9 @@
       <c r="Z166" s="9"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="121"/>
-      <c r="B167" s="122"/>
-      <c r="C167" s="123"/>
+      <c r="A167" s="128"/>
+      <c r="B167" s="129"/>
+      <c r="C167" s="130"/>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
@@ -7013,9 +7079,9 @@
       <c r="Z167" s="9"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="121"/>
-      <c r="B168" s="122"/>
-      <c r="C168" s="123"/>
+      <c r="A168" s="128"/>
+      <c r="B168" s="129"/>
+      <c r="C168" s="130"/>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
@@ -7041,9 +7107,9 @@
       <c r="Z168" s="9"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="121"/>
-      <c r="B169" s="122"/>
-      <c r="C169" s="123"/>
+      <c r="A169" s="128"/>
+      <c r="B169" s="129"/>
+      <c r="C169" s="130"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
@@ -7069,9 +7135,9 @@
       <c r="Z169" s="9"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="121"/>
-      <c r="B170" s="122"/>
-      <c r="C170" s="123"/>
+      <c r="A170" s="128"/>
+      <c r="B170" s="129"/>
+      <c r="C170" s="130"/>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
@@ -7097,9 +7163,9 @@
       <c r="Z170" s="9"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="121"/>
-      <c r="B171" s="122"/>
-      <c r="C171" s="123"/>
+      <c r="A171" s="128"/>
+      <c r="B171" s="129"/>
+      <c r="C171" s="130"/>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
@@ -7125,9 +7191,9 @@
       <c r="Z171" s="9"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="121"/>
-      <c r="B172" s="122"/>
-      <c r="C172" s="123"/>
+      <c r="A172" s="128"/>
+      <c r="B172" s="129"/>
+      <c r="C172" s="130"/>
       <c r="D172" s="8"/>
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
@@ -7153,9 +7219,9 @@
       <c r="Z172" s="9"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="121"/>
-      <c r="B173" s="122"/>
-      <c r="C173" s="123"/>
+      <c r="A173" s="128"/>
+      <c r="B173" s="129"/>
+      <c r="C173" s="130"/>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
@@ -7181,9 +7247,9 @@
       <c r="Z173" s="9"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="121"/>
-      <c r="B174" s="122"/>
-      <c r="C174" s="123"/>
+      <c r="A174" s="128"/>
+      <c r="B174" s="129"/>
+      <c r="C174" s="130"/>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
@@ -7209,9 +7275,9 @@
       <c r="Z174" s="9"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="121"/>
-      <c r="B175" s="122"/>
-      <c r="C175" s="123"/>
+      <c r="A175" s="128"/>
+      <c r="B175" s="129"/>
+      <c r="C175" s="130"/>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
@@ -7237,9 +7303,9 @@
       <c r="Z175" s="9"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="121"/>
-      <c r="B176" s="122"/>
-      <c r="C176" s="123"/>
+      <c r="A176" s="128"/>
+      <c r="B176" s="129"/>
+      <c r="C176" s="130"/>
       <c r="D176" s="8"/>
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
@@ -7265,9 +7331,9 @@
       <c r="Z176" s="9"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="121"/>
-      <c r="B177" s="122"/>
-      <c r="C177" s="123"/>
+      <c r="A177" s="128"/>
+      <c r="B177" s="129"/>
+      <c r="C177" s="130"/>
       <c r="D177" s="8"/>
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
@@ -7293,9 +7359,9 @@
       <c r="Z177" s="9"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="121"/>
-      <c r="B178" s="122"/>
-      <c r="C178" s="123"/>
+      <c r="A178" s="128"/>
+      <c r="B178" s="129"/>
+      <c r="C178" s="130"/>
       <c r="D178" s="8"/>
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
@@ -7321,9 +7387,9 @@
       <c r="Z178" s="9"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="121"/>
-      <c r="B179" s="122"/>
-      <c r="C179" s="123"/>
+      <c r="A179" s="128"/>
+      <c r="B179" s="129"/>
+      <c r="C179" s="130"/>
       <c r="D179" s="8"/>
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
@@ -7349,9 +7415,9 @@
       <c r="Z179" s="9"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="121"/>
-      <c r="B180" s="122"/>
-      <c r="C180" s="123"/>
+      <c r="A180" s="128"/>
+      <c r="B180" s="129"/>
+      <c r="C180" s="130"/>
       <c r="D180" s="8"/>
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
@@ -7377,9 +7443,9 @@
       <c r="Z180" s="9"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="121"/>
-      <c r="B181" s="122"/>
-      <c r="C181" s="123"/>
+      <c r="A181" s="128"/>
+      <c r="B181" s="129"/>
+      <c r="C181" s="130"/>
       <c r="D181" s="8"/>
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
@@ -7405,9 +7471,9 @@
       <c r="Z181" s="9"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="121"/>
-      <c r="B182" s="122"/>
-      <c r="C182" s="123"/>
+      <c r="A182" s="128"/>
+      <c r="B182" s="129"/>
+      <c r="C182" s="130"/>
       <c r="D182" s="8"/>
       <c r="E182" s="8"/>
       <c r="F182" s="8"/>
@@ -7433,9 +7499,9 @@
       <c r="Z182" s="9"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="121"/>
-      <c r="B183" s="122"/>
-      <c r="C183" s="123"/>
+      <c r="A183" s="128"/>
+      <c r="B183" s="129"/>
+      <c r="C183" s="130"/>
       <c r="D183" s="8"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
@@ -7461,9 +7527,9 @@
       <c r="Z183" s="9"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="121"/>
-      <c r="B184" s="122"/>
-      <c r="C184" s="123"/>
+      <c r="A184" s="128"/>
+      <c r="B184" s="129"/>
+      <c r="C184" s="130"/>
       <c r="D184" s="8"/>
       <c r="E184" s="8"/>
       <c r="F184" s="8"/>
@@ -7489,9 +7555,9 @@
       <c r="Z184" s="9"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="121"/>
-      <c r="B185" s="122"/>
-      <c r="C185" s="123"/>
+      <c r="A185" s="128"/>
+      <c r="B185" s="129"/>
+      <c r="C185" s="130"/>
       <c r="D185" s="8"/>
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
@@ -7517,9 +7583,9 @@
       <c r="Z185" s="9"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="121"/>
-      <c r="B186" s="122"/>
-      <c r="C186" s="123"/>
+      <c r="A186" s="128"/>
+      <c r="B186" s="129"/>
+      <c r="C186" s="130"/>
       <c r="D186" s="8"/>
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
@@ -7545,9 +7611,9 @@
       <c r="Z186" s="9"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="121"/>
-      <c r="B187" s="122"/>
-      <c r="C187" s="123"/>
+      <c r="A187" s="128"/>
+      <c r="B187" s="129"/>
+      <c r="C187" s="130"/>
       <c r="D187" s="8"/>
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
@@ -7573,9 +7639,9 @@
       <c r="Z187" s="9"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="121"/>
-      <c r="B188" s="122"/>
-      <c r="C188" s="123"/>
+      <c r="A188" s="128"/>
+      <c r="B188" s="129"/>
+      <c r="C188" s="130"/>
       <c r="D188" s="8"/>
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
@@ -7601,9 +7667,9 @@
       <c r="Z188" s="9"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="121"/>
-      <c r="B189" s="122"/>
-      <c r="C189" s="123"/>
+      <c r="A189" s="128"/>
+      <c r="B189" s="129"/>
+      <c r="C189" s="130"/>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
@@ -7629,9 +7695,9 @@
       <c r="Z189" s="9"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="121"/>
-      <c r="B190" s="122"/>
-      <c r="C190" s="123"/>
+      <c r="A190" s="128"/>
+      <c r="B190" s="129"/>
+      <c r="C190" s="130"/>
       <c r="D190" s="8"/>
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
@@ -7657,9 +7723,9 @@
       <c r="Z190" s="9"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="121"/>
-      <c r="B191" s="122"/>
-      <c r="C191" s="123"/>
+      <c r="A191" s="128"/>
+      <c r="B191" s="129"/>
+      <c r="C191" s="130"/>
       <c r="D191" s="8"/>
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
@@ -7685,9 +7751,9 @@
       <c r="Z191" s="9"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="121"/>
-      <c r="B192" s="122"/>
-      <c r="C192" s="123"/>
+      <c r="A192" s="128"/>
+      <c r="B192" s="129"/>
+      <c r="C192" s="130"/>
       <c r="D192" s="8"/>
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
@@ -7713,9 +7779,9 @@
       <c r="Z192" s="9"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="121"/>
-      <c r="B193" s="122"/>
-      <c r="C193" s="123"/>
+      <c r="A193" s="128"/>
+      <c r="B193" s="129"/>
+      <c r="C193" s="130"/>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
@@ -7741,9 +7807,9 @@
       <c r="Z193" s="9"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="121"/>
-      <c r="B194" s="122"/>
-      <c r="C194" s="123"/>
+      <c r="A194" s="128"/>
+      <c r="B194" s="129"/>
+      <c r="C194" s="130"/>
       <c r="D194" s="8"/>
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
@@ -7769,9 +7835,9 @@
       <c r="Z194" s="9"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="121"/>
-      <c r="B195" s="122"/>
-      <c r="C195" s="123"/>
+      <c r="A195" s="128"/>
+      <c r="B195" s="129"/>
+      <c r="C195" s="130"/>
       <c r="D195" s="8"/>
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
@@ -7797,9 +7863,9 @@
       <c r="Z195" s="9"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="121"/>
-      <c r="B196" s="122"/>
-      <c r="C196" s="123"/>
+      <c r="A196" s="128"/>
+      <c r="B196" s="129"/>
+      <c r="C196" s="130"/>
       <c r="D196" s="8"/>
       <c r="E196" s="8"/>
       <c r="F196" s="8"/>
@@ -7825,9 +7891,9 @@
       <c r="Z196" s="9"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="121"/>
-      <c r="B197" s="122"/>
-      <c r="C197" s="123"/>
+      <c r="A197" s="128"/>
+      <c r="B197" s="129"/>
+      <c r="C197" s="130"/>
       <c r="D197" s="8"/>
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
@@ -7853,9 +7919,9 @@
       <c r="Z197" s="9"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="121"/>
-      <c r="B198" s="122"/>
-      <c r="C198" s="123"/>
+      <c r="A198" s="128"/>
+      <c r="B198" s="129"/>
+      <c r="C198" s="130"/>
       <c r="D198" s="8"/>
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
@@ -7881,9 +7947,9 @@
       <c r="Z198" s="9"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="121"/>
-      <c r="B199" s="122"/>
-      <c r="C199" s="123"/>
+      <c r="A199" s="128"/>
+      <c r="B199" s="129"/>
+      <c r="C199" s="130"/>
       <c r="D199" s="8"/>
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
@@ -7909,9 +7975,9 @@
       <c r="Z199" s="9"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="121"/>
-      <c r="B200" s="122"/>
-      <c r="C200" s="123"/>
+      <c r="A200" s="128"/>
+      <c r="B200" s="129"/>
+      <c r="C200" s="130"/>
       <c r="D200" s="8"/>
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
@@ -7937,9 +8003,9 @@
       <c r="Z200" s="9"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="121"/>
-      <c r="B201" s="122"/>
-      <c r="C201" s="123"/>
+      <c r="A201" s="128"/>
+      <c r="B201" s="129"/>
+      <c r="C201" s="130"/>
       <c r="D201" s="8"/>
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
@@ -7965,9 +8031,9 @@
       <c r="Z201" s="9"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="121"/>
-      <c r="B202" s="122"/>
-      <c r="C202" s="123"/>
+      <c r="A202" s="128"/>
+      <c r="B202" s="129"/>
+      <c r="C202" s="130"/>
       <c r="D202" s="8"/>
       <c r="E202" s="8"/>
       <c r="F202" s="8"/>
@@ -7993,9 +8059,9 @@
       <c r="Z202" s="9"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="121"/>
-      <c r="B203" s="122"/>
-      <c r="C203" s="123"/>
+      <c r="A203" s="128"/>
+      <c r="B203" s="129"/>
+      <c r="C203" s="130"/>
       <c r="D203" s="8"/>
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
@@ -8021,9 +8087,9 @@
       <c r="Z203" s="9"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="121"/>
-      <c r="B204" s="122"/>
-      <c r="C204" s="123"/>
+      <c r="A204" s="128"/>
+      <c r="B204" s="129"/>
+      <c r="C204" s="130"/>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
       <c r="F204" s="8"/>
@@ -8049,9 +8115,9 @@
       <c r="Z204" s="9"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="121"/>
-      <c r="B205" s="122"/>
-      <c r="C205" s="123"/>
+      <c r="A205" s="128"/>
+      <c r="B205" s="129"/>
+      <c r="C205" s="130"/>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
@@ -8077,9 +8143,9 @@
       <c r="Z205" s="9"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="121"/>
-      <c r="B206" s="122"/>
-      <c r="C206" s="123"/>
+      <c r="A206" s="128"/>
+      <c r="B206" s="129"/>
+      <c r="C206" s="130"/>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
@@ -8105,9 +8171,9 @@
       <c r="Z206" s="9"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="121"/>
-      <c r="B207" s="122"/>
-      <c r="C207" s="123"/>
+      <c r="A207" s="128"/>
+      <c r="B207" s="129"/>
+      <c r="C207" s="130"/>
       <c r="D207" s="8"/>
       <c r="E207" s="8"/>
       <c r="F207" s="8"/>
@@ -8133,9 +8199,9 @@
       <c r="Z207" s="9"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="121"/>
-      <c r="B208" s="122"/>
-      <c r="C208" s="123"/>
+      <c r="A208" s="128"/>
+      <c r="B208" s="129"/>
+      <c r="C208" s="130"/>
       <c r="D208" s="8"/>
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
@@ -8161,9 +8227,9 @@
       <c r="Z208" s="9"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="121"/>
-      <c r="B209" s="122"/>
-      <c r="C209" s="123"/>
+      <c r="A209" s="128"/>
+      <c r="B209" s="129"/>
+      <c r="C209" s="130"/>
       <c r="D209" s="8"/>
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
@@ -8189,9 +8255,9 @@
       <c r="Z209" s="9"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="121"/>
-      <c r="B210" s="122"/>
-      <c r="C210" s="123"/>
+      <c r="A210" s="128"/>
+      <c r="B210" s="129"/>
+      <c r="C210" s="130"/>
       <c r="D210" s="8"/>
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
@@ -8217,9 +8283,9 @@
       <c r="Z210" s="9"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="121"/>
-      <c r="B211" s="122"/>
-      <c r="C211" s="123"/>
+      <c r="A211" s="128"/>
+      <c r="B211" s="129"/>
+      <c r="C211" s="130"/>
       <c r="D211" s="8"/>
       <c r="E211" s="8"/>
       <c r="F211" s="8"/>
@@ -8245,9 +8311,9 @@
       <c r="Z211" s="9"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="121"/>
-      <c r="B212" s="122"/>
-      <c r="C212" s="123"/>
+      <c r="A212" s="128"/>
+      <c r="B212" s="129"/>
+      <c r="C212" s="130"/>
       <c r="D212" s="8"/>
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
@@ -8273,9 +8339,9 @@
       <c r="Z212" s="9"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="121"/>
-      <c r="B213" s="122"/>
-      <c r="C213" s="123"/>
+      <c r="A213" s="128"/>
+      <c r="B213" s="129"/>
+      <c r="C213" s="130"/>
       <c r="D213" s="8"/>
       <c r="E213" s="8"/>
       <c r="F213" s="8"/>
@@ -8301,9 +8367,9 @@
       <c r="Z213" s="9"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="121"/>
-      <c r="B214" s="122"/>
-      <c r="C214" s="123"/>
+      <c r="A214" s="128"/>
+      <c r="B214" s="129"/>
+      <c r="C214" s="130"/>
       <c r="D214" s="8"/>
       <c r="E214" s="8"/>
       <c r="F214" s="8"/>
@@ -8329,9 +8395,9 @@
       <c r="Z214" s="9"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="121"/>
-      <c r="B215" s="122"/>
-      <c r="C215" s="123"/>
+      <c r="A215" s="128"/>
+      <c r="B215" s="129"/>
+      <c r="C215" s="130"/>
       <c r="D215" s="8"/>
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
@@ -8357,9 +8423,9 @@
       <c r="Z215" s="9"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="121"/>
-      <c r="B216" s="122"/>
-      <c r="C216" s="123"/>
+      <c r="A216" s="128"/>
+      <c r="B216" s="129"/>
+      <c r="C216" s="130"/>
       <c r="D216" s="8"/>
       <c r="E216" s="8"/>
       <c r="F216" s="8"/>
@@ -8385,9 +8451,9 @@
       <c r="Z216" s="9"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="121"/>
-      <c r="B217" s="122"/>
-      <c r="C217" s="123"/>
+      <c r="A217" s="128"/>
+      <c r="B217" s="129"/>
+      <c r="C217" s="130"/>
       <c r="D217" s="8"/>
       <c r="E217" s="8"/>
       <c r="F217" s="8"/>
@@ -8413,9 +8479,9 @@
       <c r="Z217" s="9"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="121"/>
-      <c r="B218" s="122"/>
-      <c r="C218" s="123"/>
+      <c r="A218" s="128"/>
+      <c r="B218" s="129"/>
+      <c r="C218" s="130"/>
       <c r="D218" s="8"/>
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
@@ -8441,9 +8507,9 @@
       <c r="Z218" s="9"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="121"/>
-      <c r="B219" s="122"/>
-      <c r="C219" s="123"/>
+      <c r="A219" s="128"/>
+      <c r="B219" s="129"/>
+      <c r="C219" s="130"/>
       <c r="D219" s="8"/>
       <c r="E219" s="8"/>
       <c r="F219" s="8"/>
@@ -8469,9 +8535,9 @@
       <c r="Z219" s="9"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="121"/>
-      <c r="B220" s="122"/>
-      <c r="C220" s="123"/>
+      <c r="A220" s="128"/>
+      <c r="B220" s="129"/>
+      <c r="C220" s="130"/>
       <c r="D220" s="8"/>
       <c r="E220" s="8"/>
       <c r="F220" s="8"/>
@@ -8497,9 +8563,9 @@
       <c r="Z220" s="9"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="121"/>
-      <c r="B221" s="122"/>
-      <c r="C221" s="123"/>
+      <c r="A221" s="128"/>
+      <c r="B221" s="129"/>
+      <c r="C221" s="130"/>
       <c r="D221" s="8"/>
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
@@ -8525,9 +8591,9 @@
       <c r="Z221" s="9"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="121"/>
-      <c r="B222" s="122"/>
-      <c r="C222" s="123"/>
+      <c r="A222" s="128"/>
+      <c r="B222" s="129"/>
+      <c r="C222" s="130"/>
       <c r="D222" s="8"/>
       <c r="E222" s="8"/>
       <c r="F222" s="8"/>
@@ -8553,9 +8619,9 @@
       <c r="Z222" s="9"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="121"/>
-      <c r="B223" s="122"/>
-      <c r="C223" s="123"/>
+      <c r="A223" s="128"/>
+      <c r="B223" s="129"/>
+      <c r="C223" s="130"/>
       <c r="D223" s="8"/>
       <c r="E223" s="8"/>
       <c r="F223" s="8"/>
@@ -8581,9 +8647,9 @@
       <c r="Z223" s="9"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="121"/>
-      <c r="B224" s="122"/>
-      <c r="C224" s="123"/>
+      <c r="A224" s="128"/>
+      <c r="B224" s="129"/>
+      <c r="C224" s="130"/>
       <c r="D224" s="8"/>
       <c r="E224" s="8"/>
       <c r="F224" s="8"/>
@@ -8609,9 +8675,9 @@
       <c r="Z224" s="9"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="121"/>
-      <c r="B225" s="122"/>
-      <c r="C225" s="123"/>
+      <c r="A225" s="128"/>
+      <c r="B225" s="129"/>
+      <c r="C225" s="130"/>
       <c r="D225" s="8"/>
       <c r="E225" s="8"/>
       <c r="F225" s="8"/>
@@ -8637,9 +8703,9 @@
       <c r="Z225" s="9"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="121"/>
-      <c r="B226" s="122"/>
-      <c r="C226" s="123"/>
+      <c r="A226" s="128"/>
+      <c r="B226" s="129"/>
+      <c r="C226" s="130"/>
       <c r="D226" s="8"/>
       <c r="E226" s="8"/>
       <c r="F226" s="8"/>
@@ -8665,9 +8731,9 @@
       <c r="Z226" s="9"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="121"/>
-      <c r="B227" s="122"/>
-      <c r="C227" s="123"/>
+      <c r="A227" s="128"/>
+      <c r="B227" s="129"/>
+      <c r="C227" s="130"/>
       <c r="D227" s="8"/>
       <c r="E227" s="8"/>
       <c r="F227" s="8"/>
@@ -8693,9 +8759,9 @@
       <c r="Z227" s="9"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="121"/>
-      <c r="B228" s="122"/>
-      <c r="C228" s="123"/>
+      <c r="A228" s="128"/>
+      <c r="B228" s="129"/>
+      <c r="C228" s="130"/>
       <c r="D228" s="8"/>
       <c r="E228" s="8"/>
       <c r="F228" s="8"/>
@@ -8721,9 +8787,9 @@
       <c r="Z228" s="9"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="121"/>
-      <c r="B229" s="122"/>
-      <c r="C229" s="123"/>
+      <c r="A229" s="128"/>
+      <c r="B229" s="129"/>
+      <c r="C229" s="130"/>
       <c r="D229" s="8"/>
       <c r="E229" s="8"/>
       <c r="F229" s="8"/>
@@ -8749,9 +8815,9 @@
       <c r="Z229" s="9"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="121"/>
-      <c r="B230" s="122"/>
-      <c r="C230" s="123"/>
+      <c r="A230" s="128"/>
+      <c r="B230" s="129"/>
+      <c r="C230" s="130"/>
       <c r="D230" s="8"/>
       <c r="E230" s="8"/>
       <c r="F230" s="8"/>
@@ -8777,9 +8843,9 @@
       <c r="Z230" s="9"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="121"/>
-      <c r="B231" s="122"/>
-      <c r="C231" s="123"/>
+      <c r="A231" s="128"/>
+      <c r="B231" s="129"/>
+      <c r="C231" s="130"/>
       <c r="D231" s="8"/>
       <c r="E231" s="8"/>
       <c r="F231" s="8"/>
@@ -8805,9 +8871,9 @@
       <c r="Z231" s="9"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="121"/>
-      <c r="B232" s="122"/>
-      <c r="C232" s="123"/>
+      <c r="A232" s="128"/>
+      <c r="B232" s="129"/>
+      <c r="C232" s="130"/>
       <c r="D232" s="8"/>
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
@@ -8833,9 +8899,9 @@
       <c r="Z232" s="9"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="121"/>
-      <c r="B233" s="122"/>
-      <c r="C233" s="123"/>
+      <c r="A233" s="128"/>
+      <c r="B233" s="129"/>
+      <c r="C233" s="130"/>
       <c r="D233" s="8"/>
       <c r="E233" s="8"/>
       <c r="F233" s="8"/>
@@ -8861,9 +8927,9 @@
       <c r="Z233" s="9"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="121"/>
-      <c r="B234" s="122"/>
-      <c r="C234" s="123"/>
+      <c r="A234" s="128"/>
+      <c r="B234" s="129"/>
+      <c r="C234" s="130"/>
       <c r="D234" s="8"/>
       <c r="E234" s="8"/>
       <c r="F234" s="8"/>
@@ -8889,9 +8955,9 @@
       <c r="Z234" s="9"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="121"/>
-      <c r="B235" s="122"/>
-      <c r="C235" s="123"/>
+      <c r="A235" s="128"/>
+      <c r="B235" s="129"/>
+      <c r="C235" s="130"/>
       <c r="D235" s="8"/>
       <c r="E235" s="8"/>
       <c r="F235" s="8"/>
@@ -8917,9 +8983,9 @@
       <c r="Z235" s="9"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="121"/>
-      <c r="B236" s="122"/>
-      <c r="C236" s="123"/>
+      <c r="A236" s="128"/>
+      <c r="B236" s="129"/>
+      <c r="C236" s="130"/>
       <c r="D236" s="8"/>
       <c r="E236" s="8"/>
       <c r="F236" s="8"/>
@@ -8945,9 +9011,9 @@
       <c r="Z236" s="9"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="121"/>
-      <c r="B237" s="122"/>
-      <c r="C237" s="123"/>
+      <c r="A237" s="128"/>
+      <c r="B237" s="129"/>
+      <c r="C237" s="130"/>
       <c r="D237" s="8"/>
       <c r="E237" s="8"/>
       <c r="F237" s="8"/>
@@ -8973,9 +9039,9 @@
       <c r="Z237" s="9"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="121"/>
-      <c r="B238" s="122"/>
-      <c r="C238" s="123"/>
+      <c r="A238" s="128"/>
+      <c r="B238" s="129"/>
+      <c r="C238" s="130"/>
       <c r="D238" s="8"/>
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
@@ -9001,9 +9067,9 @@
       <c r="Z238" s="9"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="121"/>
-      <c r="B239" s="122"/>
-      <c r="C239" s="123"/>
+      <c r="A239" s="128"/>
+      <c r="B239" s="129"/>
+      <c r="C239" s="130"/>
       <c r="D239" s="8"/>
       <c r="E239" s="8"/>
       <c r="F239" s="8"/>
@@ -9029,9 +9095,9 @@
       <c r="Z239" s="9"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="121"/>
-      <c r="B240" s="122"/>
-      <c r="C240" s="123"/>
+      <c r="A240" s="128"/>
+      <c r="B240" s="129"/>
+      <c r="C240" s="130"/>
       <c r="D240" s="8"/>
       <c r="E240" s="8"/>
       <c r="F240" s="8"/>
@@ -9057,9 +9123,9 @@
       <c r="Z240" s="9"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="121"/>
-      <c r="B241" s="122"/>
-      <c r="C241" s="123"/>
+      <c r="A241" s="128"/>
+      <c r="B241" s="129"/>
+      <c r="C241" s="130"/>
       <c r="D241" s="8"/>
       <c r="E241" s="8"/>
       <c r="F241" s="8"/>
@@ -9085,9 +9151,9 @@
       <c r="Z241" s="9"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="121"/>
-      <c r="B242" s="122"/>
-      <c r="C242" s="123"/>
+      <c r="A242" s="128"/>
+      <c r="B242" s="129"/>
+      <c r="C242" s="130"/>
       <c r="D242" s="8"/>
       <c r="E242" s="8"/>
       <c r="F242" s="8"/>
@@ -9113,9 +9179,9 @@
       <c r="Z242" s="9"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="121"/>
-      <c r="B243" s="122"/>
-      <c r="C243" s="123"/>
+      <c r="A243" s="128"/>
+      <c r="B243" s="129"/>
+      <c r="C243" s="130"/>
       <c r="D243" s="8"/>
       <c r="E243" s="8"/>
       <c r="F243" s="8"/>
@@ -9141,9 +9207,9 @@
       <c r="Z243" s="9"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="121"/>
-      <c r="B244" s="122"/>
-      <c r="C244" s="123"/>
+      <c r="A244" s="128"/>
+      <c r="B244" s="129"/>
+      <c r="C244" s="130"/>
       <c r="D244" s="8"/>
       <c r="E244" s="8"/>
       <c r="F244" s="8"/>
@@ -9169,9 +9235,9 @@
       <c r="Z244" s="9"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="121"/>
-      <c r="B245" s="122"/>
-      <c r="C245" s="123"/>
+      <c r="A245" s="128"/>
+      <c r="B245" s="129"/>
+      <c r="C245" s="130"/>
       <c r="D245" s="8"/>
       <c r="E245" s="8"/>
       <c r="F245" s="8"/>
@@ -9197,9 +9263,9 @@
       <c r="Z245" s="9"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="121"/>
-      <c r="B246" s="122"/>
-      <c r="C246" s="123"/>
+      <c r="A246" s="128"/>
+      <c r="B246" s="129"/>
+      <c r="C246" s="130"/>
       <c r="D246" s="8"/>
       <c r="E246" s="8"/>
       <c r="F246" s="8"/>
@@ -9225,9 +9291,9 @@
       <c r="Z246" s="9"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="121"/>
-      <c r="B247" s="122"/>
-      <c r="C247" s="123"/>
+      <c r="A247" s="128"/>
+      <c r="B247" s="129"/>
+      <c r="C247" s="130"/>
       <c r="D247" s="8"/>
       <c r="E247" s="8"/>
       <c r="F247" s="8"/>
@@ -9253,9 +9319,9 @@
       <c r="Z247" s="9"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="121"/>
-      <c r="B248" s="122"/>
-      <c r="C248" s="123"/>
+      <c r="A248" s="128"/>
+      <c r="B248" s="129"/>
+      <c r="C248" s="130"/>
       <c r="D248" s="8"/>
       <c r="E248" s="8"/>
       <c r="F248" s="8"/>
@@ -9281,9 +9347,9 @@
       <c r="Z248" s="9"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="121"/>
-      <c r="B249" s="122"/>
-      <c r="C249" s="123"/>
+      <c r="A249" s="128"/>
+      <c r="B249" s="129"/>
+      <c r="C249" s="130"/>
       <c r="D249" s="8"/>
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
@@ -9309,9 +9375,9 @@
       <c r="Z249" s="9"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="121"/>
-      <c r="B250" s="122"/>
-      <c r="C250" s="123"/>
+      <c r="A250" s="128"/>
+      <c r="B250" s="129"/>
+      <c r="C250" s="130"/>
       <c r="D250" s="8"/>
       <c r="E250" s="8"/>
       <c r="F250" s="8"/>
@@ -9337,9 +9403,9 @@
       <c r="Z250" s="9"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="121"/>
-      <c r="B251" s="122"/>
-      <c r="C251" s="123"/>
+      <c r="A251" s="128"/>
+      <c r="B251" s="129"/>
+      <c r="C251" s="130"/>
       <c r="D251" s="8"/>
       <c r="E251" s="8"/>
       <c r="F251" s="8"/>
@@ -9365,9 +9431,9 @@
       <c r="Z251" s="9"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="121"/>
-      <c r="B252" s="122"/>
-      <c r="C252" s="123"/>
+      <c r="A252" s="128"/>
+      <c r="B252" s="129"/>
+      <c r="C252" s="130"/>
       <c r="D252" s="8"/>
       <c r="E252" s="8"/>
       <c r="F252" s="8"/>
@@ -9393,9 +9459,9 @@
       <c r="Z252" s="9"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="121"/>
-      <c r="B253" s="122"/>
-      <c r="C253" s="123"/>
+      <c r="A253" s="128"/>
+      <c r="B253" s="129"/>
+      <c r="C253" s="130"/>
       <c r="D253" s="8"/>
       <c r="E253" s="8"/>
       <c r="F253" s="8"/>
@@ -9421,9 +9487,9 @@
       <c r="Z253" s="9"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="121"/>
-      <c r="B254" s="122"/>
-      <c r="C254" s="123"/>
+      <c r="A254" s="128"/>
+      <c r="B254" s="129"/>
+      <c r="C254" s="130"/>
       <c r="D254" s="8"/>
       <c r="E254" s="8"/>
       <c r="F254" s="8"/>
@@ -9449,9 +9515,9 @@
       <c r="Z254" s="9"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="121"/>
-      <c r="B255" s="122"/>
-      <c r="C255" s="123"/>
+      <c r="A255" s="128"/>
+      <c r="B255" s="129"/>
+      <c r="C255" s="130"/>
       <c r="D255" s="8"/>
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
@@ -9477,9 +9543,9 @@
       <c r="Z255" s="9"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="121"/>
-      <c r="B256" s="122"/>
-      <c r="C256" s="123"/>
+      <c r="A256" s="128"/>
+      <c r="B256" s="129"/>
+      <c r="C256" s="130"/>
       <c r="D256" s="8"/>
       <c r="E256" s="8"/>
       <c r="F256" s="8"/>
@@ -9505,9 +9571,9 @@
       <c r="Z256" s="9"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="121"/>
-      <c r="B257" s="122"/>
-      <c r="C257" s="123"/>
+      <c r="A257" s="128"/>
+      <c r="B257" s="129"/>
+      <c r="C257" s="130"/>
       <c r="D257" s="8"/>
       <c r="E257" s="8"/>
       <c r="F257" s="8"/>
@@ -9533,9 +9599,9 @@
       <c r="Z257" s="9"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="121"/>
-      <c r="B258" s="122"/>
-      <c r="C258" s="123"/>
+      <c r="A258" s="128"/>
+      <c r="B258" s="129"/>
+      <c r="C258" s="130"/>
       <c r="D258" s="8"/>
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
@@ -9561,9 +9627,9 @@
       <c r="Z258" s="9"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="121"/>
-      <c r="B259" s="122"/>
-      <c r="C259" s="123"/>
+      <c r="A259" s="128"/>
+      <c r="B259" s="129"/>
+      <c r="C259" s="130"/>
       <c r="D259" s="8"/>
       <c r="E259" s="8"/>
       <c r="F259" s="8"/>
@@ -9589,9 +9655,9 @@
       <c r="Z259" s="9"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="121"/>
-      <c r="B260" s="122"/>
-      <c r="C260" s="123"/>
+      <c r="A260" s="128"/>
+      <c r="B260" s="129"/>
+      <c r="C260" s="130"/>
       <c r="D260" s="8"/>
       <c r="E260" s="8"/>
       <c r="F260" s="8"/>
@@ -9617,9 +9683,9 @@
       <c r="Z260" s="9"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="121"/>
-      <c r="B261" s="122"/>
-      <c r="C261" s="123"/>
+      <c r="A261" s="128"/>
+      <c r="B261" s="129"/>
+      <c r="C261" s="130"/>
       <c r="D261" s="8"/>
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
@@ -9645,9 +9711,9 @@
       <c r="Z261" s="9"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="121"/>
-      <c r="B262" s="122"/>
-      <c r="C262" s="123"/>
+      <c r="A262" s="128"/>
+      <c r="B262" s="129"/>
+      <c r="C262" s="130"/>
       <c r="D262" s="8"/>
       <c r="E262" s="8"/>
       <c r="F262" s="8"/>
@@ -9673,82 +9739,88 @@
       <c r="Z262" s="9"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="124"/>
-      <c r="B263" s="125"/>
-      <c r="C263" s="126"/>
-      <c r="D263" s="127"/>
-      <c r="E263" s="127"/>
-      <c r="F263" s="127"/>
-      <c r="G263" s="127"/>
-      <c r="H263" s="127"/>
-      <c r="I263" s="127"/>
-      <c r="J263" s="127"/>
-      <c r="K263" s="127"/>
-      <c r="L263" s="127"/>
-      <c r="M263" s="127"/>
-      <c r="N263" s="127"/>
-      <c r="O263" s="127"/>
-      <c r="P263" s="127"/>
-      <c r="Q263" s="127"/>
-      <c r="R263" s="127"/>
-      <c r="S263" s="127"/>
-      <c r="T263" s="127"/>
-      <c r="U263" s="127"/>
-      <c r="V263" s="127"/>
-      <c r="W263" s="127"/>
-      <c r="X263" s="127"/>
-      <c r="Y263" s="127"/>
+      <c r="A263" s="128"/>
+      <c r="B263" s="129"/>
+      <c r="C263" s="130"/>
+      <c r="D263" s="8"/>
+      <c r="E263" s="8"/>
+      <c r="F263" s="8"/>
+      <c r="G263" s="8"/>
+      <c r="H263" s="8"/>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="8"/>
+      <c r="L263" s="8"/>
+      <c r="M263" s="8"/>
+      <c r="N263" s="8"/>
+      <c r="O263" s="8"/>
+      <c r="P263" s="8"/>
+      <c r="Q263" s="8"/>
+      <c r="R263" s="8"/>
+      <c r="S263" s="8"/>
+      <c r="T263" s="8"/>
+      <c r="U263" s="8"/>
+      <c r="V263" s="8"/>
+      <c r="W263" s="8"/>
+      <c r="X263" s="8"/>
+      <c r="Y263" s="8"/>
       <c r="Z263" s="9"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="52"/>
-      <c r="B264" s="52"/>
-      <c r="C264" s="52"/>
-      <c r="D264" s="52"/>
-      <c r="E264" s="52"/>
-      <c r="F264" s="52"/>
-      <c r="G264" s="52"/>
-      <c r="H264" s="52"/>
-      <c r="I264" s="52"/>
-      <c r="J264" s="52"/>
-      <c r="K264" s="52"/>
-      <c r="L264" s="52"/>
-      <c r="M264" s="52"/>
-      <c r="N264" s="52"/>
-      <c r="O264" s="52"/>
-      <c r="P264" s="52"/>
-      <c r="Q264" s="52"/>
-      <c r="R264" s="52"/>
-      <c r="S264" s="52"/>
-      <c r="T264" s="52"/>
-      <c r="U264" s="52"/>
-      <c r="V264" s="52"/>
-      <c r="W264" s="52"/>
+      <c r="A264" s="128"/>
+      <c r="B264" s="129"/>
+      <c r="C264" s="130"/>
+      <c r="D264" s="8"/>
+      <c r="E264" s="8"/>
+      <c r="F264" s="8"/>
+      <c r="G264" s="8"/>
+      <c r="H264" s="8"/>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="8"/>
+      <c r="L264" s="8"/>
+      <c r="M264" s="8"/>
+      <c r="N264" s="8"/>
+      <c r="O264" s="8"/>
+      <c r="P264" s="8"/>
+      <c r="Q264" s="8"/>
+      <c r="R264" s="8"/>
+      <c r="S264" s="8"/>
+      <c r="T264" s="8"/>
+      <c r="U264" s="8"/>
+      <c r="V264" s="8"/>
+      <c r="W264" s="8"/>
+      <c r="X264" s="8"/>
+      <c r="Y264" s="8"/>
+      <c r="Z264" s="9"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="52"/>
-      <c r="B265" s="52"/>
-      <c r="C265" s="52"/>
-      <c r="D265" s="52"/>
-      <c r="E265" s="52"/>
-      <c r="F265" s="52"/>
-      <c r="G265" s="52"/>
-      <c r="H265" s="52"/>
-      <c r="I265" s="52"/>
-      <c r="J265" s="52"/>
-      <c r="K265" s="52"/>
-      <c r="L265" s="52"/>
-      <c r="M265" s="52"/>
-      <c r="N265" s="52"/>
-      <c r="O265" s="52"/>
-      <c r="P265" s="52"/>
-      <c r="Q265" s="52"/>
-      <c r="R265" s="52"/>
-      <c r="S265" s="52"/>
-      <c r="T265" s="52"/>
-      <c r="U265" s="52"/>
-      <c r="V265" s="52"/>
-      <c r="W265" s="52"/>
+      <c r="A265" s="131"/>
+      <c r="B265" s="132"/>
+      <c r="C265" s="133"/>
+      <c r="D265" s="134"/>
+      <c r="E265" s="134"/>
+      <c r="F265" s="134"/>
+      <c r="G265" s="134"/>
+      <c r="H265" s="134"/>
+      <c r="I265" s="134"/>
+      <c r="J265" s="134"/>
+      <c r="K265" s="134"/>
+      <c r="L265" s="134"/>
+      <c r="M265" s="134"/>
+      <c r="N265" s="134"/>
+      <c r="O265" s="134"/>
+      <c r="P265" s="134"/>
+      <c r="Q265" s="134"/>
+      <c r="R265" s="134"/>
+      <c r="S265" s="134"/>
+      <c r="T265" s="134"/>
+      <c r="U265" s="134"/>
+      <c r="V265" s="134"/>
+      <c r="W265" s="134"/>
+      <c r="X265" s="134"/>
+      <c r="Y265" s="134"/>
+      <c r="Z265" s="9"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="52"/>
@@ -28250,117 +28322,177 @@
       <c r="V1005" s="52"/>
       <c r="W1005" s="52"/>
     </row>
+    <row r="1006" ht="15.75" customHeight="1">
+      <c r="A1006" s="52"/>
+      <c r="B1006" s="52"/>
+      <c r="C1006" s="52"/>
+      <c r="D1006" s="52"/>
+      <c r="E1006" s="52"/>
+      <c r="F1006" s="52"/>
+      <c r="G1006" s="52"/>
+      <c r="H1006" s="52"/>
+      <c r="I1006" s="52"/>
+      <c r="J1006" s="52"/>
+      <c r="K1006" s="52"/>
+      <c r="L1006" s="52"/>
+      <c r="M1006" s="52"/>
+      <c r="N1006" s="52"/>
+      <c r="O1006" s="52"/>
+      <c r="P1006" s="52"/>
+      <c r="Q1006" s="52"/>
+      <c r="R1006" s="52"/>
+      <c r="S1006" s="52"/>
+      <c r="T1006" s="52"/>
+      <c r="U1006" s="52"/>
+      <c r="V1006" s="52"/>
+      <c r="W1006" s="52"/>
+    </row>
+    <row r="1007" ht="15.75" customHeight="1">
+      <c r="A1007" s="52"/>
+      <c r="B1007" s="52"/>
+      <c r="C1007" s="52"/>
+      <c r="D1007" s="52"/>
+      <c r="E1007" s="52"/>
+      <c r="F1007" s="52"/>
+      <c r="G1007" s="52"/>
+      <c r="H1007" s="52"/>
+      <c r="I1007" s="52"/>
+      <c r="J1007" s="52"/>
+      <c r="K1007" s="52"/>
+      <c r="L1007" s="52"/>
+      <c r="M1007" s="52"/>
+      <c r="N1007" s="52"/>
+      <c r="O1007" s="52"/>
+      <c r="P1007" s="52"/>
+      <c r="Q1007" s="52"/>
+      <c r="R1007" s="52"/>
+      <c r="S1007" s="52"/>
+      <c r="T1007" s="52"/>
+      <c r="U1007" s="52"/>
+      <c r="V1007" s="52"/>
+      <c r="W1007" s="52"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B48">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$B21="Long"</formula>
+      <formula>$B28="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B48">
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$B21="Short"</formula>
+      <formula>$B28="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B49">
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>AND($B21="Long",$B27="Limit")</formula>
+      <formula>AND($B28="Long",$B29="Limit")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B49">
     <cfRule type="expression" dxfId="1" priority="4">
-      <formula>AND($B21="Short",$B27="Limit")</formula>
+      <formula>AND($B28="Short",$B29="Limit")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>$B28="Long"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>$B28="Short"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>AND($B28="Long",$B29="Limit")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>AND($B28="Short",$B29="Limit")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="expression" dxfId="1" priority="9">
+      <formula>$B28="Long"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>$B28="Short"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$B21="Long"</formula>
+    <cfRule type="expression" dxfId="1" priority="11">
+      <formula>$B28="Long"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50">
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>$B21="Short"</formula>
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>$B28="Short"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="expression" dxfId="3" priority="13">
+      <formula>$B29="Market"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="expression" dxfId="1" priority="7">
-      <formula>AND($B21="Long",$B27="Limit")</formula>
+    <cfRule type="expression" dxfId="0" priority="14">
+      <formula>AND($B28="Short",$B29="Limit")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>AND($B21="Short",$B27="Limit")</formula>
+    <cfRule type="expression" dxfId="1" priority="15">
+      <formula>AND($B28="Long",$B29="Limit")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="expression" dxfId="1" priority="9">
-      <formula>$B21="Long"</formula>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="expression" dxfId="4" priority="16">
+      <formula>$B28="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="expression" dxfId="0" priority="10">
-      <formula>$B21="Short"</formula>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="expression" dxfId="1" priority="17">
+      <formula>$B28="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="expression" dxfId="1" priority="11">
-      <formula>$B21="Long"</formula>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="expression" dxfId="1" priority="18">
+      <formula>$B28="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="expression" dxfId="0" priority="12">
-      <formula>$B21="Short"</formula>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="cellIs" dxfId="5" priority="19" operator="equal">
+      <formula>"Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A47">
-    <cfRule type="expression" dxfId="3" priority="13">
-      <formula>$B27="Market"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="expression" dxfId="0" priority="14">
-      <formula>AND($B21="Short",$B27="Limit")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="expression" dxfId="1" priority="15">
-      <formula>AND($B21="Long",$B27="Limit")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="expression" dxfId="4" priority="16">
-      <formula>$B21="Short"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="expression" dxfId="1" priority="17">
-      <formula>$B21="Long"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="expression" dxfId="1" priority="18">
-      <formula>$B21="Long"</formula>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="cellIs" dxfId="6" priority="20" operator="equal">
+      <formula>"Short"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B27">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B29">
       <formula1>"Limit,Market"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B21">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B28">
       <formula1>"Long,Short"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B28">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B27">
+      <formula1>"EVB,NSE Topers"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B30">
       <formula1>"Normal,Strong"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B22">
-      <formula1>"EVB,BTR,NSE Topers"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
@@ -28385,61 +28517,61 @@
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
-      <c r="B1" s="17" t="str">
+      <c r="B1" s="11" t="str">
         <f>'Position Calculator'!$B$20</f>
-        <v>TRANSRAILL</v>
+        <v/>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>9</v>
+      <c r="C1" s="12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17" t="str">
+        <f>'Position Calculator'!$B$28</f>
+        <v>Long</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="32.25" customHeight="1">
+      <c r="A3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="20" t="str">
-        <f>'Position Calculator'!$B$21</f>
-        <v>Short</v>
+      <c r="B3" s="22">
+        <v>1229.0</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="32.25" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="25">
-        <v>470.15</v>
+    </row>
+    <row r="4" ht="32.25" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>13</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="B4" s="25">
+        <f>IFERROR(IF(B2="Long",B3-'Position Calculator'!B16*'Position Calculator'!B32,B3+'Position Calculator'!B16*'Position Calculator'!B32),0)</f>
+        <v>1229</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="32.25" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>16</v>
+    <row r="5" ht="42.0" customHeight="1">
+      <c r="A5" s="26" t="s">
+        <v>15</v>
       </c>
-      <c r="B4" s="32">
-        <f>IFERROR(IF(B2="Long",B3-'Position Calculator'!B16*'Position Calculator'!B30,B3+'Position Calculator'!B16*'Position Calculator'!B30),0)</f>
-        <v>470.3</v>
+      <c r="B5" s="27">
+        <f>IFERROR(IF(B2="Short", B4+'Position Calculator'!B32*'Position Calculator'!B17, B4-'Position Calculator'!B32*'Position Calculator'!B17),0)</f>
+        <v>1229</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="39">
-        <f>IFERROR(IF(B2="Short", B4+'Position Calculator'!B30*'Position Calculator'!B17, B4-'Position Calculator'!B30*'Position Calculator'!B17),0)</f>
-        <v>470.7</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>20</v>
+      <c r="C5" s="28" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
